--- a/data/Activos_promedio.xlsx
+++ b/data/Activos_promedio.xlsx
@@ -38,6 +38,9 @@
     <t xml:space="preserve">BAC</t>
   </si>
   <si>
+    <t xml:space="preserve">BANCO FICOHSA</t>
+  </si>
+  <si>
     <t xml:space="preserve">BANCORP</t>
   </si>
   <si>
@@ -56,9 +59,6 @@
     <t xml:space="preserve">FDL</t>
   </si>
   <si>
-    <t xml:space="preserve">FICOHSA</t>
-  </si>
-  <si>
     <t xml:space="preserve">FINCA</t>
   </si>
   <si>
@@ -72,9 +72,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd hh:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -111,7 +109,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -649,7 +647,7 @@
         <v>20.2986826044704</v>
       </c>
       <c r="E16" t="n">
-        <v>16.1644815199023</v>
+        <v>16.1644815199024</v>
       </c>
     </row>
     <row r="17">
@@ -1006,7 +1004,7 @@
         <v>34.8156365881418</v>
       </c>
       <c r="E37" t="n">
-        <v>28.9656107272261</v>
+        <v>28.9656107272262</v>
       </c>
     </row>
     <row r="38">
@@ -1278,7 +1276,7 @@
         <v>58.5718752527693</v>
       </c>
       <c r="E53" t="n">
-        <v>48.0671063278578</v>
+        <v>48.0671063278579</v>
       </c>
     </row>
     <row r="54">
@@ -1448,7 +1446,7 @@
         <v>62.6199920459913</v>
       </c>
       <c r="E63" t="n">
-        <v>61.6421949720996</v>
+        <v>61.6421949720995</v>
       </c>
     </row>
     <row r="64">
@@ -1499,7 +1497,7 @@
         <v>64.5966806038614</v>
       </c>
       <c r="E66" t="n">
-        <v>63.2356468622381</v>
+        <v>63.235646862238</v>
       </c>
     </row>
     <row r="67">
@@ -1783,7 +1781,7 @@
         <v>160.909735532753</v>
       </c>
       <c r="E84" t="n">
-        <v>164.349702646278</v>
+        <v>164.349702646277</v>
       </c>
     </row>
     <row r="85">
@@ -1834,7 +1832,7 @@
         <v>158.883439830491</v>
       </c>
       <c r="E87" t="n">
-        <v>161.057874667467</v>
+        <v>161.057874667466</v>
       </c>
     </row>
     <row r="88">
@@ -1970,7 +1968,7 @@
         <v>176.051557275925</v>
       </c>
       <c r="E95" t="n">
-        <v>165.863763037067</v>
+        <v>165.863763037066</v>
       </c>
     </row>
     <row r="96">
@@ -2412,7 +2410,7 @@
         <v>249.048764724446</v>
       </c>
       <c r="E121" t="n">
-        <v>237.342868233303</v>
+        <v>237.342868233304</v>
       </c>
     </row>
     <row r="122">
@@ -3189,7 +3187,7 @@
         <v>1528.8889952578</v>
       </c>
       <c r="E168" t="n">
-        <v>1516.18455421305</v>
+        <v>1516.18455421304</v>
       </c>
     </row>
     <row r="169">
@@ -3206,7 +3204,7 @@
         <v>1537.1454188987</v>
       </c>
       <c r="E169" t="n">
-        <v>1520.38049381842</v>
+        <v>1520.38049381841</v>
       </c>
     </row>
     <row r="170">
@@ -3750,7 +3748,7 @@
         <v>2033.14979664775</v>
       </c>
       <c r="E201" t="n">
-        <v>1951.73296051728</v>
+        <v>1951.73296051727</v>
       </c>
     </row>
     <row r="202">
@@ -3835,7 +3833,7 @@
         <v>2138.82474259057</v>
       </c>
       <c r="E206" t="n">
-        <v>2049.22813606546</v>
+        <v>2049.22813606545</v>
       </c>
     </row>
     <row r="207">
@@ -3869,7 +3867,7 @@
         <v>2186.27614979535</v>
       </c>
       <c r="E208" t="n">
-        <v>2086.92536501582</v>
+        <v>2086.92536501581</v>
       </c>
     </row>
     <row r="209">
@@ -3937,7 +3935,7 @@
         <v>2236.41642407582</v>
       </c>
       <c r="E212" t="n">
-        <v>2149.08506895158</v>
+        <v>2149.08506895157</v>
       </c>
     </row>
     <row r="213">
@@ -4070,7 +4068,7 @@
         <v>10</v>
       </c>
       <c r="D220" t="n">
-        <v>386.155358996387</v>
+        <v>412.817884216087</v>
       </c>
       <c r="E220"/>
     </row>
@@ -4085,7 +4083,7 @@
         <v>10</v>
       </c>
       <c r="D221" t="n">
-        <v>354.976236704157</v>
+        <v>396.209781519341</v>
       </c>
       <c r="E221"/>
     </row>
@@ -4100,7 +4098,7 @@
         <v>10</v>
       </c>
       <c r="D222" t="n">
-        <v>303.810684960967</v>
+        <v>390.522691912943</v>
       </c>
       <c r="E222"/>
     </row>
@@ -4115,7 +4113,7 @@
         <v>10</v>
       </c>
       <c r="D223" t="n">
-        <v>273.306006514414</v>
+        <v>397.893359864306</v>
       </c>
       <c r="E223"/>
     </row>
@@ -4130,7 +4128,7 @@
         <v>10</v>
       </c>
       <c r="D224" t="n">
-        <v>222.652614289309</v>
+        <v>407.153238657217</v>
       </c>
       <c r="E224"/>
     </row>
@@ -4145,1176 +4143,1188 @@
         <v>10</v>
       </c>
       <c r="D225" t="n">
-        <v>200.744275515515</v>
+        <v>401.157472570662</v>
       </c>
       <c r="E225"/>
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B226" s="1" t="n">
-        <v>43496</v>
+        <v>43677</v>
       </c>
       <c r="C226" t="n">
         <v>10</v>
       </c>
       <c r="D226" t="n">
-        <v>1882.50883232095</v>
+        <v>380.078264807365</v>
       </c>
       <c r="E226"/>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B227" s="1" t="n">
-        <v>43524</v>
+        <v>43708</v>
       </c>
       <c r="C227" t="n">
         <v>10</v>
       </c>
       <c r="D227" t="n">
-        <v>1901.63414414773</v>
+        <v>381.754817118344</v>
       </c>
       <c r="E227"/>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B228" s="1" t="n">
-        <v>43555</v>
+        <v>43738</v>
       </c>
       <c r="C228" t="n">
         <v>10</v>
       </c>
       <c r="D228" t="n">
-        <v>1908.7177409672</v>
+        <v>387.45680748447</v>
       </c>
       <c r="E228"/>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B229" s="1" t="n">
-        <v>43585</v>
+        <v>43769</v>
       </c>
       <c r="C229" t="n">
         <v>10</v>
       </c>
       <c r="D229" t="n">
-        <v>1894.58718002423</v>
+        <v>396.039517789037</v>
       </c>
       <c r="E229"/>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B230" s="1" t="n">
-        <v>43616</v>
+        <v>43799</v>
       </c>
       <c r="C230" t="n">
         <v>10</v>
       </c>
       <c r="D230" t="n">
-        <v>1891.48172297232</v>
+        <v>403.389872196782</v>
       </c>
       <c r="E230"/>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B231" s="1" t="n">
-        <v>43646</v>
+        <v>43830</v>
       </c>
       <c r="C231" t="n">
         <v>10</v>
       </c>
       <c r="D231" t="n">
-        <v>1891.79908598281</v>
-      </c>
-      <c r="E231"/>
+        <v>407.25857631424</v>
+      </c>
+      <c r="E231" t="n">
+        <v>396.811023704233</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B232" s="1" t="n">
-        <v>43677</v>
+        <v>43861</v>
       </c>
       <c r="C232" t="n">
         <v>10</v>
       </c>
       <c r="D232" t="n">
-        <v>1911.42438518632</v>
-      </c>
-      <c r="E232"/>
+        <v>411.332588889511</v>
+      </c>
+      <c r="E232" t="n">
+        <v>396.687249093685</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B233" s="1" t="n">
-        <v>43708</v>
+        <v>43890</v>
       </c>
       <c r="C233" t="n">
         <v>10</v>
       </c>
       <c r="D233" t="n">
-        <v>1897.78694074265</v>
-      </c>
-      <c r="E233"/>
+        <v>416.625160709244</v>
+      </c>
+      <c r="E233" t="n">
+        <v>398.388530692843</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B234" s="1" t="n">
-        <v>43738</v>
+        <v>43921</v>
       </c>
       <c r="C234" t="n">
         <v>10</v>
       </c>
       <c r="D234" t="n">
-        <v>2011.24107870309</v>
-      </c>
-      <c r="E234"/>
+        <v>424.774808548245</v>
+      </c>
+      <c r="E234" t="n">
+        <v>401.242873745785</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B235" s="1" t="n">
-        <v>43769</v>
+        <v>43951</v>
       </c>
       <c r="C235" t="n">
         <v>10</v>
       </c>
       <c r="D235" t="n">
-        <v>1957.47336679249</v>
-      </c>
-      <c r="E235"/>
+        <v>446.704185306581</v>
+      </c>
+      <c r="E235" t="n">
+        <v>405.310442532642</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B236" s="1" t="n">
-        <v>43799</v>
+        <v>43982</v>
       </c>
       <c r="C236" t="n">
         <v>10</v>
       </c>
       <c r="D236" t="n">
-        <v>2058.05661995709</v>
-      </c>
-      <c r="E236"/>
+        <v>441.728312947805</v>
+      </c>
+      <c r="E236" t="n">
+        <v>408.191698723524</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B237" s="1" t="n">
-        <v>43830</v>
+        <v>44012</v>
       </c>
       <c r="C237" t="n">
         <v>10</v>
       </c>
       <c r="D237" t="n">
-        <v>1990.32919916421</v>
+        <v>445.232083763989</v>
       </c>
       <c r="E237" t="n">
-        <v>1933.08669141342</v>
+        <v>411.864582989634</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B238" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C238" t="n">
         <v>10</v>
       </c>
       <c r="D238" t="n">
-        <v>2017.92491687061</v>
+        <v>431.173839294761</v>
       </c>
       <c r="E238" t="n">
-        <v>1944.3713651259</v>
+        <v>416.122547530251</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B239" s="1" t="n">
-        <v>43890</v>
+        <v>44074</v>
       </c>
       <c r="C239" t="n">
         <v>10</v>
       </c>
       <c r="D239" t="n">
-        <v>2029.64299822042</v>
+        <v>439.621632714023</v>
       </c>
       <c r="E239" t="n">
-        <v>1955.03876963195</v>
+        <v>420.944782163224</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B240" s="1" t="n">
-        <v>43921</v>
+        <v>44104</v>
       </c>
       <c r="C240" t="n">
         <v>10</v>
       </c>
       <c r="D240" t="n">
-        <v>2025.53491440402</v>
+        <v>465.753697542433</v>
       </c>
       <c r="E240" t="n">
-        <v>1964.77353408502</v>
+        <v>427.469523001388</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B241" s="1" t="n">
-        <v>43951</v>
+        <v>44135</v>
       </c>
       <c r="C241" t="n">
         <v>10</v>
       </c>
       <c r="D241" t="n">
-        <v>2002.67118005789</v>
+        <v>464.03577482462</v>
       </c>
       <c r="E241" t="n">
-        <v>1973.78053408783</v>
+        <v>433.135877754353</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B242" s="1" t="n">
-        <v>43982</v>
+        <v>44165</v>
       </c>
       <c r="C242" t="n">
         <v>10</v>
       </c>
       <c r="D242" t="n">
-        <v>2006.46608581358</v>
+        <v>469.046247471819</v>
       </c>
       <c r="E242" t="n">
-        <v>1983.3625643246</v>
+        <v>438.607242360606</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B243" s="1" t="n">
-        <v>44012</v>
+        <v>44196</v>
       </c>
       <c r="C243" t="n">
         <v>10</v>
       </c>
       <c r="D243" t="n">
-        <v>1991.94854061667</v>
+        <v>476.971523413689</v>
       </c>
       <c r="E243" t="n">
-        <v>1991.70835221075</v>
+        <v>444.416654618893</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B244" s="1" t="n">
-        <v>44043</v>
+        <v>44227</v>
       </c>
       <c r="C244" t="n">
         <v>10</v>
       </c>
       <c r="D244" t="n">
-        <v>2017.8557811333</v>
+        <v>491.463027568651</v>
       </c>
       <c r="E244" t="n">
-        <v>2000.57763520633</v>
+        <v>451.094191175488</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B245" s="1" t="n">
-        <v>44074</v>
+        <v>44255</v>
       </c>
       <c r="C245" t="n">
         <v>10</v>
       </c>
       <c r="D245" t="n">
-        <v>2037.08154979065</v>
+        <v>485.854331500654</v>
       </c>
       <c r="E245" t="n">
-        <v>2012.18551929367</v>
+        <v>456.863288741439</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B246" s="1" t="n">
-        <v>44104</v>
+        <v>44286</v>
       </c>
       <c r="C246" t="n">
         <v>10</v>
       </c>
       <c r="D246" t="n">
-        <v>2036.33117899593</v>
+        <v>494.88296510663</v>
       </c>
       <c r="E246" t="n">
-        <v>2014.27636098474</v>
+        <v>462.705635121305</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B247" s="1" t="n">
-        <v>44135</v>
+        <v>44316</v>
       </c>
       <c r="C247" t="n">
         <v>10</v>
       </c>
       <c r="D247" t="n">
-        <v>2047.34233746854</v>
+        <v>493.881982300246</v>
       </c>
       <c r="E247" t="n">
-        <v>2021.76544187441</v>
+        <v>466.63711820411</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B248" s="1" t="n">
-        <v>44165</v>
+        <v>44347</v>
       </c>
       <c r="C248" t="n">
         <v>10</v>
       </c>
       <c r="D248" t="n">
-        <v>2096.78459230342</v>
+        <v>509.628290443377</v>
       </c>
       <c r="E248" t="n">
-        <v>2024.99277290327</v>
+        <v>472.295449662074</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B249" s="1" t="n">
-        <v>44196</v>
+        <v>44377</v>
       </c>
       <c r="C249" t="n">
         <v>10</v>
       </c>
       <c r="D249" t="n">
-        <v>2100.0362725874</v>
+        <v>519.601716605958</v>
       </c>
       <c r="E249" t="n">
-        <v>2034.13502902187</v>
+        <v>478.492919065572</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B250" s="1" t="n">
-        <v>44227</v>
+        <v>44408</v>
       </c>
       <c r="C250" t="n">
         <v>10</v>
       </c>
       <c r="D250" t="n">
-        <v>2076.33346394386</v>
+        <v>516.937506249131</v>
       </c>
       <c r="E250" t="n">
-        <v>2039.00240794464</v>
+        <v>485.639891311769</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B251" s="1" t="n">
-        <v>44255</v>
+        <v>44439</v>
       </c>
       <c r="C251" t="n">
         <v>10</v>
       </c>
       <c r="D251" t="n">
-        <v>2117.29805922212</v>
+        <v>520.527024985972</v>
       </c>
       <c r="E251" t="n">
-        <v>2046.30699636145</v>
+        <v>492.382007334432</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B252" s="1" t="n">
-        <v>44286</v>
+        <v>44469</v>
       </c>
       <c r="C252" t="n">
         <v>10</v>
       </c>
       <c r="D252" t="n">
-        <v>2131.56906615964</v>
+        <v>515.442469851828</v>
       </c>
       <c r="E252" t="n">
-        <v>2055.14317567442</v>
+        <v>496.522738360215</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B253" s="1" t="n">
-        <v>44316</v>
+        <v>44500</v>
       </c>
       <c r="C253" t="n">
         <v>10</v>
       </c>
       <c r="D253" t="n">
-        <v>2167.50517928158</v>
+        <v>524.994910636489</v>
       </c>
       <c r="E253" t="n">
-        <v>2068.87934227639</v>
+        <v>501.602666344537</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B254" s="1" t="n">
-        <v>44347</v>
+        <v>44530</v>
       </c>
       <c r="C254" t="n">
         <v>10</v>
       </c>
       <c r="D254" t="n">
-        <v>2141.95978740177</v>
+        <v>526.259524120097</v>
       </c>
       <c r="E254" t="n">
-        <v>2080.17048407541</v>
+        <v>506.37043939856</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B255" s="1" t="n">
-        <v>44377</v>
+        <v>44561</v>
       </c>
       <c r="C255" t="n">
         <v>10</v>
       </c>
       <c r="D255" t="n">
-        <v>2149.89199599836</v>
+        <v>534.066355287013</v>
       </c>
       <c r="E255" t="n">
-        <v>2093.33243869055</v>
+        <v>511.12834205467</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B256" s="1" t="n">
-        <v>44408</v>
+        <v>44592</v>
       </c>
       <c r="C256" t="n">
         <v>10</v>
       </c>
       <c r="D256" t="n">
-        <v>2196.56096941633</v>
+        <v>551.41334486955</v>
       </c>
       <c r="E256" t="n">
-        <v>2108.22453771413</v>
+        <v>516.124201829745</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B257" s="1" t="n">
-        <v>44439</v>
+        <v>44620</v>
       </c>
       <c r="C257" t="n">
         <v>10</v>
       </c>
       <c r="D257" t="n">
-        <v>2210.00045945543</v>
+        <v>565.648740374858</v>
       </c>
       <c r="E257" t="n">
-        <v>2122.63444685287</v>
+        <v>522.773735902596</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B258" s="1" t="n">
-        <v>44469</v>
+        <v>44651</v>
       </c>
       <c r="C258" t="n">
         <v>10</v>
       </c>
       <c r="D258" t="n">
-        <v>2188.87974961931</v>
+        <v>541.827258679976</v>
       </c>
       <c r="E258" t="n">
-        <v>2135.34682773815</v>
+        <v>526.685760367041</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B259" s="1" t="n">
-        <v>44500</v>
+        <v>44681</v>
       </c>
       <c r="C259" t="n">
         <v>10</v>
       </c>
       <c r="D259" t="n">
-        <v>2239.62627603944</v>
+        <v>572.11627609767</v>
       </c>
       <c r="E259" t="n">
-        <v>2151.37048928572</v>
+        <v>533.20528485016</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B260" s="1" t="n">
-        <v>44530</v>
+        <v>44712</v>
       </c>
       <c r="C260" t="n">
         <v>10</v>
       </c>
       <c r="D260" t="n">
-        <v>2241.18933877523</v>
+        <v>568.560024403361</v>
       </c>
       <c r="E260" t="n">
-        <v>2163.40421815837</v>
+        <v>538.116262680159</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B261" s="1" t="n">
-        <v>44561</v>
+        <v>44742</v>
       </c>
       <c r="C261" t="n">
         <v>10</v>
       </c>
       <c r="D261" t="n">
-        <v>2185.65249527913</v>
+        <v>596.673521352048</v>
       </c>
       <c r="E261" t="n">
-        <v>2170.53890338268</v>
+        <v>544.538913075666</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B262" s="1" t="n">
-        <v>44592</v>
+        <v>44773</v>
       </c>
       <c r="C262" t="n">
         <v>10</v>
       </c>
       <c r="D262" t="n">
-        <v>2184.26035400849</v>
+        <v>588.38630961402</v>
       </c>
       <c r="E262" t="n">
-        <v>2179.53281088807</v>
+        <v>550.49298002274</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B263" s="1" t="n">
-        <v>44620</v>
+        <v>44804</v>
       </c>
       <c r="C263" t="n">
         <v>10</v>
       </c>
       <c r="D263" t="n">
-        <v>2233.26973649073</v>
+        <v>587.5265885206</v>
       </c>
       <c r="E263" t="n">
-        <v>2189.19711732712</v>
+        <v>556.076276983959</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B264" s="1" t="n">
-        <v>44651</v>
+        <v>44834</v>
       </c>
       <c r="C264" t="n">
         <v>10</v>
       </c>
       <c r="D264" t="n">
-        <v>2282.02120353861</v>
+        <v>580.478738543453</v>
       </c>
       <c r="E264" t="n">
-        <v>2201.73479544204</v>
+        <v>561.495966041595</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B265" s="1" t="n">
-        <v>44681</v>
+        <v>44865</v>
       </c>
       <c r="C265" t="n">
         <v>10</v>
       </c>
       <c r="D265" t="n">
-        <v>2247.18017984225</v>
+        <v>592.232176142912</v>
       </c>
       <c r="E265" t="n">
-        <v>2208.37437882209</v>
+        <v>567.099071500463</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B266" s="1" t="n">
-        <v>44712</v>
+        <v>44895</v>
       </c>
       <c r="C266" t="n">
         <v>10</v>
       </c>
       <c r="D266" t="n">
-        <v>2225.29942065194</v>
+        <v>602.774341298572</v>
       </c>
       <c r="E266" t="n">
-        <v>2215.31934825961</v>
+        <v>573.475306265336</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B267" s="1" t="n">
-        <v>44742</v>
+        <v>44926</v>
       </c>
       <c r="C267" t="n">
         <v>10</v>
       </c>
       <c r="D267" t="n">
-        <v>2218.61769362948</v>
+        <v>594.045648661934</v>
       </c>
       <c r="E267" t="n">
-        <v>2221.04648972887</v>
+        <v>578.473580713246</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B268" s="1" t="n">
-        <v>44773</v>
+        <v>44957</v>
       </c>
       <c r="C268" t="n">
         <v>10</v>
       </c>
       <c r="D268" t="n">
-        <v>2243.05210043694</v>
+        <v>608.24277687108</v>
       </c>
       <c r="E268" t="n">
-        <v>2224.92075064725</v>
+        <v>583.209366713374</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B269" s="1" t="n">
-        <v>44804</v>
+        <v>44985</v>
       </c>
       <c r="C269" t="n">
         <v>10</v>
       </c>
       <c r="D269" t="n">
-        <v>2251.20078208783</v>
+        <v>619.395300307819</v>
       </c>
       <c r="E269" t="n">
-        <v>2228.35411086662</v>
+        <v>587.688246707787</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B270" s="1" t="n">
-        <v>44834</v>
+        <v>45016</v>
       </c>
       <c r="C270" t="n">
         <v>10</v>
       </c>
       <c r="D270" t="n">
-        <v>2266.95135825053</v>
+        <v>627.326646036676</v>
       </c>
       <c r="E270" t="n">
-        <v>2234.86007825255</v>
+        <v>594.813195654179</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B271" s="1" t="n">
-        <v>44865</v>
+        <v>45046</v>
       </c>
       <c r="C271" t="n">
         <v>10</v>
       </c>
       <c r="D271" t="n">
-        <v>2288.87482140193</v>
+        <v>616.245382351534</v>
       </c>
       <c r="E271" t="n">
-        <v>2238.96412369943</v>
+        <v>598.490621175334</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B272" s="1" t="n">
-        <v>44895</v>
+        <v>45077</v>
       </c>
       <c r="C272" t="n">
         <v>10</v>
       </c>
       <c r="D272" t="n">
-        <v>2297.21981331804</v>
+        <v>637.584540565154</v>
       </c>
       <c r="E272" t="n">
-        <v>2243.63332991133</v>
+        <v>604.242664188817</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B273" s="1" t="n">
-        <v>44926</v>
+        <v>45107</v>
       </c>
       <c r="C273" t="n">
         <v>10</v>
       </c>
       <c r="D273" t="n">
-        <v>2254.6473475949</v>
+        <v>668.908690629811</v>
       </c>
       <c r="E273" t="n">
-        <v>2249.38290093764</v>
+        <v>610.26226162863</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B274" s="1" t="n">
-        <v>44957</v>
+        <v>45138</v>
       </c>
       <c r="C274" t="n">
         <v>10</v>
       </c>
       <c r="D274" t="n">
-        <v>2322.64983484963</v>
+        <v>655.204695938517</v>
       </c>
       <c r="E274" t="n">
-        <v>2260.9153576744</v>
+        <v>615.830460489005</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B275" s="1" t="n">
-        <v>44985</v>
+        <v>45169</v>
       </c>
       <c r="C275" t="n">
         <v>10</v>
       </c>
       <c r="D275" t="n">
-        <v>2372.52851519654</v>
+        <v>697.894933491495</v>
       </c>
       <c r="E275" t="n">
-        <v>2272.52025589989</v>
+        <v>625.027822569913</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B276" s="1" t="n">
-        <v>45016</v>
+        <v>45199</v>
       </c>
       <c r="C276" t="n">
         <v>10</v>
       </c>
       <c r="D276" t="n">
-        <v>2342.70054894445</v>
+        <v>676.856114915719</v>
       </c>
       <c r="E276" t="n">
-        <v>2277.57686801704</v>
+        <v>633.059270600935</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B277" s="1" t="n">
-        <v>45046</v>
+        <v>45230</v>
       </c>
       <c r="C277" t="n">
         <v>10</v>
       </c>
       <c r="D277" t="n">
-        <v>2346.3113432795</v>
+        <v>692.539150966401</v>
       </c>
       <c r="E277" t="n">
-        <v>2285.83779830348</v>
+        <v>641.418185169559</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B278" s="1" t="n">
-        <v>45077</v>
+        <v>45260</v>
       </c>
       <c r="C278" t="n">
         <v>10</v>
       </c>
       <c r="D278" t="n">
-        <v>2378.70325862356</v>
+        <v>713.855889224286</v>
       </c>
       <c r="E278" t="n">
-        <v>2298.62145146778</v>
+        <v>650.674980830035</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B279" s="1" t="n">
-        <v>45107</v>
+        <v>45291</v>
       </c>
       <c r="C279" t="n">
         <v>10</v>
       </c>
       <c r="D279" t="n">
-        <v>2398.37830659311</v>
+        <v>710.769912069582</v>
       </c>
       <c r="E279" t="n">
-        <v>2313.60150254808</v>
+        <v>660.402002780673</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B280" s="1" t="n">
-        <v>45138</v>
+        <v>45322</v>
       </c>
       <c r="C280" t="n">
         <v>10</v>
       </c>
       <c r="D280" t="n">
-        <v>2399.37778449875</v>
+        <v>705.447095046458</v>
       </c>
       <c r="E280" t="n">
-        <v>2326.62864288657</v>
+        <v>668.502362628621</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B281" s="1" t="n">
-        <v>45169</v>
+        <v>45351</v>
       </c>
       <c r="C281" t="n">
         <v>10</v>
       </c>
       <c r="D281" t="n">
-        <v>2404.26608808691</v>
+        <v>712.762144593343</v>
       </c>
       <c r="E281" t="n">
-        <v>2339.38408505315</v>
+        <v>676.282932985748</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B282" s="1" t="n">
-        <v>45199</v>
+        <v>45382</v>
       </c>
       <c r="C282" t="n">
         <v>10</v>
       </c>
       <c r="D282" t="n">
-        <v>2394.08919588176</v>
+        <v>702.130595938762</v>
       </c>
       <c r="E282" t="n">
-        <v>2349.97890485576</v>
+        <v>682.516595477588</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B283" s="1" t="n">
-        <v>45230</v>
+        <v>45412</v>
       </c>
       <c r="C283" t="n">
         <v>10</v>
       </c>
       <c r="D283" t="n">
-        <v>2416.2970984542</v>
+        <v>715.217725407448</v>
       </c>
       <c r="E283" t="n">
-        <v>2360.59742794345</v>
+        <v>690.764290732248</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B284" s="1" t="n">
-        <v>45260</v>
+        <v>45443</v>
       </c>
       <c r="C284" t="n">
         <v>10</v>
       </c>
       <c r="D284" t="n">
-        <v>2542.95033992359</v>
+        <v>730.297790337836</v>
       </c>
       <c r="E284" t="n">
-        <v>2381.07497182724</v>
+        <v>698.490394879972</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B285" s="1" t="n">
-        <v>45291</v>
+        <v>45473</v>
       </c>
       <c r="C285" t="n">
         <v>10</v>
       </c>
       <c r="D285" t="n">
-        <v>2501.82271304025</v>
+        <v>746.919487920315</v>
       </c>
       <c r="E285" t="n">
-        <v>2401.67291894769</v>
+        <v>704.99129465418</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B286" s="1" t="n">
-        <v>45322</v>
+        <v>45504</v>
       </c>
       <c r="C286" t="n">
         <v>10</v>
       </c>
       <c r="D286" t="n">
-        <v>2560.85779661946</v>
+        <v>717.952534310826</v>
       </c>
       <c r="E286" t="n">
-        <v>2421.52358242851</v>
+        <v>710.220281185206</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B287" s="1" t="n">
-        <v>45351</v>
+        <v>45535</v>
       </c>
       <c r="C287" t="n">
         <v>10</v>
       </c>
       <c r="D287" t="n">
-        <v>2561.67163761246</v>
+        <v>749.170131532343</v>
       </c>
       <c r="E287" t="n">
-        <v>2437.2855092965</v>
+        <v>714.493214355277</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B288" s="1" t="n">
-        <v>45382</v>
+        <v>45565</v>
       </c>
       <c r="C288" t="n">
         <v>10</v>
       </c>
       <c r="D288" t="n">
-        <v>2563.86935598223</v>
+        <v>742.453357047643</v>
       </c>
       <c r="E288" t="n">
-        <v>2455.71624321631</v>
+        <v>719.959651199604</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B289" s="1" t="n">
-        <v>45412</v>
+        <v>45596</v>
       </c>
       <c r="C289" t="n">
         <v>10</v>
       </c>
       <c r="D289" t="n">
-        <v>2599.01082240998</v>
+        <v>752.175277427282</v>
       </c>
       <c r="E289" t="n">
-        <v>2476.77453314385</v>
+        <v>724.929328404677</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B290" s="1" t="n">
-        <v>45443</v>
+        <v>45626</v>
       </c>
       <c r="C290" t="n">
         <v>10</v>
       </c>
       <c r="D290" t="n">
-        <v>2610.20667073036</v>
+        <v>747.325260246612</v>
       </c>
       <c r="E290" t="n">
-        <v>2496.06648415275</v>
+        <v>727.718442656537</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B291" s="1" t="n">
-        <v>45473</v>
+        <v>45657</v>
       </c>
       <c r="C291" t="n">
         <v>10</v>
       </c>
       <c r="D291" t="n">
-        <v>2590.54927134034</v>
+        <v>762.793090082814</v>
       </c>
       <c r="E291" t="n">
-        <v>2512.08073121502</v>
+        <v>732.053707490973</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B292" s="1" t="n">
-        <v>45504</v>
+        <v>45688</v>
       </c>
       <c r="C292" t="n">
         <v>10</v>
       </c>
       <c r="D292" t="n">
-        <v>2643.7521799491</v>
+        <v>776.93591859858</v>
       </c>
       <c r="E292" t="n">
-        <v>2532.44526416922</v>
+        <v>738.01110945365</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B293" s="1" t="n">
-        <v>45535</v>
+        <v>45716</v>
       </c>
       <c r="C293" t="n">
         <v>10</v>
       </c>
       <c r="D293" t="n">
-        <v>2627.79852496321</v>
+        <v>769.92813945386</v>
       </c>
       <c r="E293" t="n">
-        <v>2551.07296724224</v>
+        <v>742.774942358693</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B294" s="1" t="n">
-        <v>45565</v>
+        <v>45747</v>
       </c>
       <c r="C294" t="n">
         <v>10</v>
       </c>
       <c r="D294" t="n">
-        <v>2626.29963819022</v>
+        <v>788.654157951688</v>
       </c>
       <c r="E294" t="n">
-        <v>2570.42383743462</v>
+        <v>749.985239193104</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B295" s="1" t="n">
-        <v>45596</v>
+        <v>45777</v>
       </c>
       <c r="C295" t="n">
         <v>10</v>
       </c>
       <c r="D295" t="n">
-        <v>2638.2429104589</v>
+        <v>797.363651571224</v>
       </c>
       <c r="E295" t="n">
-        <v>2588.91932176834</v>
+        <v>756.830733040085</v>
       </c>
     </row>
     <row r="296">
@@ -5322,102 +5332,90 @@
         <v>9</v>
       </c>
       <c r="B296" s="1" t="n">
-        <v>45626</v>
+        <v>43496</v>
       </c>
       <c r="C296" t="n">
         <v>10</v>
       </c>
       <c r="D296" t="n">
-        <v>2713.03738722296</v>
-      </c>
-      <c r="E296" t="n">
-        <v>2603.09324237662</v>
-      </c>
+        <v>386.155358996387</v>
+      </c>
+      <c r="E296"/>
     </row>
     <row r="297">
       <c r="A297" t="s">
         <v>9</v>
       </c>
       <c r="B297" s="1" t="n">
-        <v>45657</v>
+        <v>43524</v>
       </c>
       <c r="C297" t="n">
         <v>10</v>
       </c>
       <c r="D297" t="n">
-        <v>2681.7821791895</v>
-      </c>
-      <c r="E297" t="n">
-        <v>2618.08986455573</v>
-      </c>
+        <v>354.976236704157</v>
+      </c>
+      <c r="E297"/>
     </row>
     <row r="298">
       <c r="A298" t="s">
         <v>9</v>
       </c>
       <c r="B298" s="1" t="n">
-        <v>45688</v>
+        <v>43555</v>
       </c>
       <c r="C298" t="n">
         <v>10</v>
       </c>
       <c r="D298" t="n">
-        <v>2704.52760824125</v>
-      </c>
-      <c r="E298" t="n">
-        <v>2630.06234885754</v>
-      </c>
+        <v>303.810684960967</v>
+      </c>
+      <c r="E298"/>
     </row>
     <row r="299">
       <c r="A299" t="s">
         <v>9</v>
       </c>
       <c r="B299" s="1" t="n">
-        <v>45716</v>
+        <v>43585</v>
       </c>
       <c r="C299" t="n">
         <v>10</v>
       </c>
       <c r="D299" t="n">
-        <v>2778.02630893969</v>
-      </c>
-      <c r="E299" t="n">
-        <v>2648.09190480148</v>
-      </c>
+        <v>273.306006514414</v>
+      </c>
+      <c r="E299"/>
     </row>
     <row r="300">
       <c r="A300" t="s">
         <v>9</v>
       </c>
       <c r="B300" s="1" t="n">
-        <v>45747</v>
+        <v>43616</v>
       </c>
       <c r="C300" t="n">
         <v>10</v>
       </c>
       <c r="D300" t="n">
-        <v>2781.67239967945</v>
-      </c>
-      <c r="E300" t="n">
-        <v>2666.24215844291</v>
-      </c>
+        <v>222.652614289309</v>
+      </c>
+      <c r="E300"/>
     </row>
     <row r="301">
       <c r="A301" t="s">
         <v>9</v>
       </c>
       <c r="B301" s="1" t="n">
-        <v>45777</v>
+        <v>43646</v>
       </c>
       <c r="C301" t="n">
         <v>10</v>
       </c>
       <c r="D301" t="n">
-        <v>2805.26576985335</v>
-      </c>
-      <c r="E301" t="n">
-        <v>2683.43007072986</v>
-      </c>
+        <v>200.744275515515</v>
+      </c>
+      <c r="E301"/>
     </row>
     <row r="302">
       <c r="A302" t="s">
@@ -5430,7 +5428,7 @@
         <v>10</v>
       </c>
       <c r="D302" t="n">
-        <v>669.26720825666</v>
+        <v>1882.50883232095</v>
       </c>
       <c r="E302"/>
     </row>
@@ -5445,7 +5443,7 @@
         <v>10</v>
       </c>
       <c r="D303" t="n">
-        <v>664.958315536495</v>
+        <v>1901.63414414773</v>
       </c>
       <c r="E303"/>
     </row>
@@ -5460,7 +5458,7 @@
         <v>10</v>
       </c>
       <c r="D304" t="n">
-        <v>656.846672308277</v>
+        <v>1908.7177409672</v>
       </c>
       <c r="E304"/>
     </row>
@@ -5475,7 +5473,7 @@
         <v>10</v>
       </c>
       <c r="D305" t="n">
-        <v>643.027847390673</v>
+        <v>1894.58718002423</v>
       </c>
       <c r="E305"/>
     </row>
@@ -5490,7 +5488,7 @@
         <v>10</v>
       </c>
       <c r="D306" t="n">
-        <v>632.879349111086</v>
+        <v>1891.48172297232</v>
       </c>
       <c r="E306"/>
     </row>
@@ -5505,7 +5503,7 @@
         <v>10</v>
       </c>
       <c r="D307" t="n">
-        <v>634.627685029074</v>
+        <v>1891.79908598281</v>
       </c>
       <c r="E307"/>
     </row>
@@ -5520,7 +5518,7 @@
         <v>10</v>
       </c>
       <c r="D308" t="n">
-        <v>628.465447667154</v>
+        <v>1911.42438518632</v>
       </c>
       <c r="E308"/>
     </row>
@@ -5535,7 +5533,7 @@
         <v>10</v>
       </c>
       <c r="D309" t="n">
-        <v>625.772813746785</v>
+        <v>1897.78694074265</v>
       </c>
       <c r="E309"/>
     </row>
@@ -5550,7 +5548,7 @@
         <v>10</v>
       </c>
       <c r="D310" t="n">
-        <v>629.148350899884</v>
+        <v>2011.24107870309</v>
       </c>
       <c r="E310"/>
     </row>
@@ -5565,7 +5563,7 @@
         <v>10</v>
       </c>
       <c r="D311" t="n">
-        <v>617.665167867293</v>
+        <v>1957.47336679249</v>
       </c>
       <c r="E311"/>
     </row>
@@ -5580,7 +5578,7 @@
         <v>10</v>
       </c>
       <c r="D312" t="n">
-        <v>619.465745003562</v>
+        <v>2058.05661995709</v>
       </c>
       <c r="E312"/>
     </row>
@@ -5595,10 +5593,10 @@
         <v>10</v>
       </c>
       <c r="D313" t="n">
-        <v>615.078373670658</v>
+        <v>1990.32919916421</v>
       </c>
       <c r="E313" t="n">
-        <v>636.433581373967</v>
+        <v>1933.08669141342</v>
       </c>
     </row>
     <row r="314">
@@ -5612,10 +5610,10 @@
         <v>10</v>
       </c>
       <c r="D314" t="n">
-        <v>592.592436691143</v>
+        <v>2017.92491687061</v>
       </c>
       <c r="E314" t="n">
-        <v>630.04401707684</v>
+        <v>1944.3713651259</v>
       </c>
     </row>
     <row r="315">
@@ -5629,10 +5627,10 @@
         <v>10</v>
       </c>
       <c r="D315" t="n">
-        <v>580.698904733195</v>
+        <v>2029.64299822042</v>
       </c>
       <c r="E315" t="n">
-        <v>623.022399509899</v>
+        <v>1955.03876963195</v>
       </c>
     </row>
     <row r="316">
@@ -5646,10 +5644,10 @@
         <v>10</v>
       </c>
       <c r="D316" t="n">
-        <v>568.147479480282</v>
+        <v>2025.53491440402</v>
       </c>
       <c r="E316" t="n">
-        <v>615.630800107566</v>
+        <v>1964.77353408502</v>
       </c>
     </row>
     <row r="317">
@@ -5663,10 +5661,10 @@
         <v>10</v>
       </c>
       <c r="D317" t="n">
-        <v>550.344821564278</v>
+        <v>2002.67118005789</v>
       </c>
       <c r="E317" t="n">
-        <v>607.907214622033</v>
+        <v>1973.78053408783</v>
       </c>
     </row>
     <row r="318">
@@ -5680,10 +5678,10 @@
         <v>10</v>
       </c>
       <c r="D318" t="n">
-        <v>538.183980824089</v>
+        <v>2006.46608581358</v>
       </c>
       <c r="E318" t="n">
-        <v>600.01593393145</v>
+        <v>1983.3625643246</v>
       </c>
     </row>
     <row r="319">
@@ -5697,10 +5695,10 @@
         <v>10</v>
       </c>
       <c r="D319" t="n">
-        <v>531.865344590277</v>
+        <v>1991.94854061667</v>
       </c>
       <c r="E319" t="n">
-        <v>591.45240556155</v>
+        <v>1991.70835221075</v>
       </c>
     </row>
     <row r="320">
@@ -5714,10 +5712,10 @@
         <v>10</v>
       </c>
       <c r="D320" t="n">
-        <v>532.717437480102</v>
+        <v>2017.8557811333</v>
       </c>
       <c r="E320" t="n">
-        <v>583.473404712629</v>
+        <v>2000.57763520633</v>
       </c>
     </row>
     <row r="321">
@@ -5731,10 +5729,10 @@
         <v>10</v>
       </c>
       <c r="D321" t="n">
-        <v>535.859935588427</v>
+        <v>2037.08154979065</v>
       </c>
       <c r="E321" t="n">
-        <v>575.980664866099</v>
+        <v>2012.18551929367</v>
       </c>
     </row>
     <row r="322">
@@ -5748,10 +5746,10 @@
         <v>10</v>
       </c>
       <c r="D322" t="n">
-        <v>532.734967276674</v>
+        <v>2036.33117899593</v>
       </c>
       <c r="E322" t="n">
-        <v>567.946216230832</v>
+        <v>2014.27636098474</v>
       </c>
     </row>
     <row r="323">
@@ -5765,10 +5763,10 @@
         <v>10</v>
       </c>
       <c r="D323" t="n">
-        <v>528.286621587053</v>
+        <v>2047.34233746854</v>
       </c>
       <c r="E323" t="n">
-        <v>560.498004040812</v>
+        <v>2021.76544187441</v>
       </c>
     </row>
     <row r="324">
@@ -5782,10 +5780,10 @@
         <v>10</v>
       </c>
       <c r="D324" t="n">
-        <v>527.041870323965</v>
+        <v>2096.78459230342</v>
       </c>
       <c r="E324" t="n">
-        <v>552.796014484179</v>
+        <v>2024.99277290327</v>
       </c>
     </row>
     <row r="325">
@@ -5799,10 +5797,10 @@
         <v>10</v>
       </c>
       <c r="D325" t="n">
-        <v>519.75104907723</v>
+        <v>2100.0362725874</v>
       </c>
       <c r="E325" t="n">
-        <v>544.85207076806</v>
+        <v>2034.13502902187</v>
       </c>
     </row>
     <row r="326">
@@ -5816,10 +5814,10 @@
         <v>10</v>
       </c>
       <c r="D326" t="n">
-        <v>520.937185169896</v>
+        <v>2076.33346394386</v>
       </c>
       <c r="E326" t="n">
-        <v>538.880799807956</v>
+        <v>2039.00240794464</v>
       </c>
     </row>
     <row r="327">
@@ -5833,10 +5831,10 @@
         <v>10</v>
       </c>
       <c r="D327" t="n">
-        <v>522.268338215199</v>
+        <v>2117.29805922212</v>
       </c>
       <c r="E327" t="n">
-        <v>534.011585931456</v>
+        <v>2046.30699636145</v>
       </c>
     </row>
     <row r="328">
@@ -5850,10 +5848,10 @@
         <v>10</v>
       </c>
       <c r="D328" t="n">
-        <v>521.631449201455</v>
+        <v>2131.56906615964</v>
       </c>
       <c r="E328" t="n">
-        <v>530.135250074887</v>
+        <v>2055.14317567442</v>
       </c>
     </row>
     <row r="329">
@@ -5867,10 +5865,10 @@
         <v>10</v>
       </c>
       <c r="D329" t="n">
-        <v>517.172946716155</v>
+        <v>2167.50517928158</v>
       </c>
       <c r="E329" t="n">
-        <v>527.370927170877</v>
+        <v>2068.87934227639</v>
       </c>
     </row>
     <row r="330">
@@ -5884,10 +5882,10 @@
         <v>10</v>
       </c>
       <c r="D330" t="n">
-        <v>518.523992562075</v>
+        <v>2141.95978740177</v>
       </c>
       <c r="E330" t="n">
-        <v>525.732594815709</v>
+        <v>2080.17048407541</v>
       </c>
     </row>
     <row r="331">
@@ -5901,10 +5899,10 @@
         <v>10</v>
       </c>
       <c r="D331" t="n">
-        <v>529.179447283191</v>
+        <v>2149.89199599836</v>
       </c>
       <c r="E331" t="n">
-        <v>525.508770040119</v>
+        <v>2093.33243869055</v>
       </c>
     </row>
     <row r="332">
@@ -5918,10 +5916,10 @@
         <v>10</v>
       </c>
       <c r="D332" t="n">
-        <v>524.437407781749</v>
+        <v>2196.56096941633</v>
       </c>
       <c r="E332" t="n">
-        <v>524.818767565256</v>
+        <v>2108.22453771413</v>
       </c>
     </row>
     <row r="333">
@@ -5935,10 +5933,10 @@
         <v>10</v>
       </c>
       <c r="D333" t="n">
-        <v>530.894968229583</v>
+        <v>2210.00045945543</v>
       </c>
       <c r="E333" t="n">
-        <v>524.405020285352</v>
+        <v>2122.63444685287</v>
       </c>
     </row>
     <row r="334">
@@ -5952,10 +5950,10 @@
         <v>10</v>
       </c>
       <c r="D334" t="n">
-        <v>528.264316071989</v>
+        <v>2188.87974961931</v>
       </c>
       <c r="E334" t="n">
-        <v>524.032466018295</v>
+        <v>2135.34682773815</v>
       </c>
     </row>
     <row r="335">
@@ -5969,10 +5967,10 @@
         <v>10</v>
       </c>
       <c r="D335" t="n">
-        <v>530.098819528805</v>
+        <v>2239.62627603944</v>
       </c>
       <c r="E335" t="n">
-        <v>524.183482513441</v>
+        <v>2151.37048928572</v>
       </c>
     </row>
     <row r="336">
@@ -5986,10 +5984,10 @@
         <v>10</v>
       </c>
       <c r="D336" t="n">
-        <v>531.264518772013</v>
+        <v>2241.18933877523</v>
       </c>
       <c r="E336" t="n">
-        <v>524.535369884112</v>
+        <v>2163.40421815837</v>
       </c>
     </row>
     <row r="337">
@@ -6003,10 +6001,10 @@
         <v>10</v>
       </c>
       <c r="D337" t="n">
-        <v>536.20069633963</v>
+        <v>2185.65249527913</v>
       </c>
       <c r="E337" t="n">
-        <v>525.906173822645</v>
+        <v>2170.53890338268</v>
       </c>
     </row>
     <row r="338">
@@ -6020,10 +6018,10 @@
         <v>10</v>
       </c>
       <c r="D338" t="n">
-        <v>535.358296543351</v>
+        <v>2184.26035400849</v>
       </c>
       <c r="E338" t="n">
-        <v>527.107933103766</v>
+        <v>2179.53281088807</v>
       </c>
     </row>
     <row r="339">
@@ -6037,10 +6035,10 @@
         <v>10</v>
       </c>
       <c r="D339" t="n">
-        <v>537.520117728456</v>
+        <v>2233.26973649073</v>
       </c>
       <c r="E339" t="n">
-        <v>528.378914729871</v>
+        <v>2189.19711732712</v>
       </c>
     </row>
     <row r="340">
@@ -6054,10 +6052,10 @@
         <v>10</v>
       </c>
       <c r="D340" t="n">
-        <v>544.290646174233</v>
+        <v>2282.02120353861</v>
       </c>
       <c r="E340" t="n">
-        <v>530.267181144269</v>
+        <v>2201.73479544203</v>
       </c>
     </row>
     <row r="341">
@@ -6071,10 +6069,10 @@
         <v>10</v>
       </c>
       <c r="D341" t="n">
-        <v>542.620339420748</v>
+        <v>2247.18017984225</v>
       </c>
       <c r="E341" t="n">
-        <v>532.387797202985</v>
+        <v>2208.37437882209</v>
       </c>
     </row>
     <row r="342">
@@ -6088,10 +6086,10 @@
         <v>10</v>
       </c>
       <c r="D342" t="n">
-        <v>538.144132262496</v>
+        <v>2225.29942065194</v>
       </c>
       <c r="E342" t="n">
-        <v>534.022808844687</v>
+        <v>2215.3193482596</v>
       </c>
     </row>
     <row r="343">
@@ -6105,10 +6103,10 @@
         <v>10</v>
       </c>
       <c r="D343" t="n">
-        <v>546.172486614165</v>
+        <v>2218.61769362948</v>
       </c>
       <c r="E343" t="n">
-        <v>535.438895455601</v>
+        <v>2221.04648972886</v>
       </c>
     </row>
     <row r="344">
@@ -6122,10 +6120,10 @@
         <v>10</v>
       </c>
       <c r="D344" t="n">
-        <v>536.949505622859</v>
+        <v>2243.05210043694</v>
       </c>
       <c r="E344" t="n">
-        <v>536.481570275694</v>
+        <v>2224.92075064725</v>
       </c>
     </row>
     <row r="345">
@@ -6139,10 +6137,10 @@
         <v>10</v>
       </c>
       <c r="D345" t="n">
-        <v>545.042537839482</v>
+        <v>2251.20078208783</v>
       </c>
       <c r="E345" t="n">
-        <v>537.660534409852</v>
+        <v>2228.35411086661</v>
       </c>
     </row>
     <row r="346">
@@ -6156,10 +6154,10 @@
         <v>10</v>
       </c>
       <c r="D346" t="n">
-        <v>535.748961532829</v>
+        <v>2266.95135825053</v>
       </c>
       <c r="E346" t="n">
-        <v>538.284254864922</v>
+        <v>2234.86007825255</v>
       </c>
     </row>
     <row r="347">
@@ -6173,10 +6171,10 @@
         <v>10</v>
       </c>
       <c r="D347" t="n">
-        <v>537.57802256554</v>
+        <v>2288.87482140193</v>
       </c>
       <c r="E347" t="n">
-        <v>538.90752178465</v>
+        <v>2238.96412369942</v>
       </c>
     </row>
     <row r="348">
@@ -6190,10 +6188,10 @@
         <v>10</v>
       </c>
       <c r="D348" t="n">
-        <v>536.732967670616</v>
+        <v>2297.21981331804</v>
       </c>
       <c r="E348" t="n">
-        <v>539.363225859534</v>
+        <v>2243.63332991132</v>
       </c>
     </row>
     <row r="349">
@@ -6207,10 +6205,10 @@
         <v>10</v>
       </c>
       <c r="D349" t="n">
-        <v>541.273792539344</v>
+        <v>2254.6473475949</v>
       </c>
       <c r="E349" t="n">
-        <v>539.785983876176</v>
+        <v>2249.38290093764</v>
       </c>
     </row>
     <row r="350">
@@ -6224,10 +6222,10 @@
         <v>10</v>
       </c>
       <c r="D350" t="n">
-        <v>547.106766250921</v>
+        <v>2322.64983484963</v>
       </c>
       <c r="E350" t="n">
-        <v>540.765023018474</v>
+        <v>2260.9153576744</v>
       </c>
     </row>
     <row r="351">
@@ -6241,10 +6239,10 @@
         <v>10</v>
       </c>
       <c r="D351" t="n">
-        <v>555.814445290349</v>
+        <v>2372.52851519654</v>
       </c>
       <c r="E351" t="n">
-        <v>542.289550315298</v>
+        <v>2272.52025589988</v>
       </c>
     </row>
     <row r="352">
@@ -6258,10 +6256,10 @@
         <v>10</v>
       </c>
       <c r="D352" t="n">
-        <v>551.819170429537</v>
+        <v>2342.70054894445</v>
       </c>
       <c r="E352" t="n">
-        <v>542.916927336574</v>
+        <v>2277.57686801704</v>
       </c>
     </row>
     <row r="353">
@@ -6275,10 +6273,10 @@
         <v>10</v>
       </c>
       <c r="D353" t="n">
-        <v>554.665865449073</v>
+        <v>2346.3113432795</v>
       </c>
       <c r="E353" t="n">
-        <v>543.920721172268</v>
+        <v>2285.83779830348</v>
       </c>
     </row>
     <row r="354">
@@ -6292,10 +6290,10 @@
         <v>10</v>
       </c>
       <c r="D354" t="n">
-        <v>554.59480160994</v>
+        <v>2378.70325862356</v>
       </c>
       <c r="E354" t="n">
-        <v>545.291610284555</v>
+        <v>2298.62145146778</v>
       </c>
     </row>
     <row r="355">
@@ -6309,10 +6307,10 @@
         <v>10</v>
       </c>
       <c r="D355" t="n">
-        <v>542.332984042469</v>
+        <v>2398.37830659311</v>
       </c>
       <c r="E355" t="n">
-        <v>544.971651736913</v>
+        <v>2313.60150254808</v>
       </c>
     </row>
     <row r="356">
@@ -6326,10 +6324,10 @@
         <v>10</v>
       </c>
       <c r="D356" t="n">
-        <v>549.172899110822</v>
+        <v>2399.37778449875</v>
       </c>
       <c r="E356" t="n">
-        <v>545.99026786091</v>
+        <v>2326.62864288656</v>
       </c>
     </row>
     <row r="357">
@@ -6343,10 +6341,10 @@
         <v>10</v>
       </c>
       <c r="D357" t="n">
-        <v>553.584642426177</v>
+        <v>2404.26608808691</v>
       </c>
       <c r="E357" t="n">
-        <v>546.702109909801</v>
+        <v>2339.38408505315</v>
       </c>
     </row>
     <row r="358">
@@ -6360,10 +6358,10 @@
         <v>10</v>
       </c>
       <c r="D358" t="n">
-        <v>554.339198922059</v>
+        <v>2394.08919588176</v>
       </c>
       <c r="E358" t="n">
-        <v>548.251296358904</v>
+        <v>2349.97890485576</v>
       </c>
     </row>
     <row r="359">
@@ -6377,10 +6375,10 @@
         <v>10</v>
       </c>
       <c r="D359" t="n">
-        <v>556.959435082801</v>
+        <v>2416.2970984542</v>
       </c>
       <c r="E359" t="n">
-        <v>549.866414068676</v>
+        <v>2360.59742794345</v>
       </c>
     </row>
     <row r="360">
@@ -6394,10 +6392,10 @@
         <v>10</v>
       </c>
       <c r="D360" t="n">
-        <v>566.172994095383</v>
+        <v>2542.95033992359</v>
       </c>
       <c r="E360" t="n">
-        <v>552.319749604073</v>
+        <v>2381.07497182724</v>
       </c>
     </row>
     <row r="361">
@@ -6411,10 +6409,10 @@
         <v>10</v>
       </c>
       <c r="D361" t="n">
-        <v>561.149331399098</v>
+        <v>2501.82271304025</v>
       </c>
       <c r="E361" t="n">
-        <v>553.976044509052</v>
+        <v>2401.67291894769</v>
       </c>
     </row>
     <row r="362">
@@ -6428,10 +6426,10 @@
         <v>10</v>
       </c>
       <c r="D362" t="n">
-        <v>550.800175865204</v>
+        <v>2560.85779661946</v>
       </c>
       <c r="E362" t="n">
-        <v>554.283828643576</v>
+        <v>2421.52358242851</v>
       </c>
     </row>
     <row r="363">
@@ -6445,10 +6443,10 @@
         <v>10</v>
       </c>
       <c r="D363" t="n">
-        <v>566.282634402842</v>
+        <v>2561.67163761246</v>
       </c>
       <c r="E363" t="n">
-        <v>555.156177736284</v>
+        <v>2437.2855092965</v>
       </c>
     </row>
     <row r="364">
@@ -6462,10 +6460,10 @@
         <v>10</v>
       </c>
       <c r="D364" t="n">
-        <v>573.038567362652</v>
+        <v>2563.86935598223</v>
       </c>
       <c r="E364" t="n">
-        <v>556.924460814043</v>
+        <v>2455.71624321631</v>
       </c>
     </row>
     <row r="365">
@@ -6479,10 +6477,10 @@
         <v>10</v>
       </c>
       <c r="D365" t="n">
-        <v>573.777350591274</v>
+        <v>2599.01082240998</v>
       </c>
       <c r="E365" t="n">
-        <v>558.517084575893</v>
+        <v>2476.77453314386</v>
       </c>
     </row>
     <row r="366">
@@ -6496,10 +6494,10 @@
         <v>10</v>
       </c>
       <c r="D366" t="n">
-        <v>576.220295412062</v>
+        <v>2610.20667073036</v>
       </c>
       <c r="E366" t="n">
-        <v>560.319209059404</v>
+        <v>2496.06648415276</v>
       </c>
     </row>
     <row r="367">
@@ -6513,10 +6511,10 @@
         <v>10</v>
       </c>
       <c r="D367" t="n">
-        <v>592.288917948193</v>
+        <v>2590.54927134034</v>
       </c>
       <c r="E367" t="n">
-        <v>564.482203551547</v>
+        <v>2512.08073121502</v>
       </c>
     </row>
     <row r="368">
@@ -6530,10 +6528,10 @@
         <v>10</v>
       </c>
       <c r="D368" t="n">
-        <v>586.516807615162</v>
+        <v>2643.7521799491</v>
       </c>
       <c r="E368" t="n">
-        <v>567.594195926909</v>
+        <v>2532.44526416922</v>
       </c>
     </row>
     <row r="369">
@@ -6547,10 +6545,10 @@
         <v>10</v>
       </c>
       <c r="D369" t="n">
-        <v>594.460199885595</v>
+        <v>2627.79852496321</v>
       </c>
       <c r="E369" t="n">
-        <v>571.00049238186</v>
+        <v>2551.07296724224</v>
       </c>
     </row>
     <row r="370">
@@ -6564,10 +6562,10 @@
         <v>10</v>
       </c>
       <c r="D370" t="n">
-        <v>596.341532295771</v>
+        <v>2626.29963819022</v>
       </c>
       <c r="E370" t="n">
-        <v>574.50068682967</v>
+        <v>2570.42383743462</v>
       </c>
     </row>
     <row r="371">
@@ -6581,10 +6579,10 @@
         <v>10</v>
       </c>
       <c r="D371" t="n">
-        <v>601.387165180222</v>
+        <v>2638.2429104589</v>
       </c>
       <c r="E371" t="n">
-        <v>578.202997671121</v>
+        <v>2588.91932176834</v>
       </c>
     </row>
     <row r="372">
@@ -6598,10 +6596,10 @@
         <v>10</v>
       </c>
       <c r="D372" t="n">
-        <v>602.491217667505</v>
+        <v>2713.03738722296</v>
       </c>
       <c r="E372" t="n">
-        <v>581.229516302132</v>
+        <v>2603.09324237662</v>
       </c>
     </row>
     <row r="373">
@@ -6615,10 +6613,10 @@
         <v>10</v>
       </c>
       <c r="D373" t="n">
-        <v>594.33533985414</v>
+        <v>2681.7821791895</v>
       </c>
       <c r="E373" t="n">
-        <v>583.995017006719</v>
+        <v>2618.08986455573</v>
       </c>
     </row>
     <row r="374">
@@ -6632,10 +6630,10 @@
         <v>10</v>
       </c>
       <c r="D374" t="n">
-        <v>587.877189178223</v>
+        <v>2704.52760824125</v>
       </c>
       <c r="E374" t="n">
-        <v>587.084768116137</v>
+        <v>2630.06234885754</v>
       </c>
     </row>
     <row r="375">
@@ -6649,10 +6647,10 @@
         <v>10</v>
       </c>
       <c r="D375" t="n">
-        <v>604.345206657874</v>
+        <v>2778.02630893969</v>
       </c>
       <c r="E375" t="n">
-        <v>590.256649137389</v>
+        <v>2648.09190480148</v>
       </c>
     </row>
     <row r="376">
@@ -6666,10 +6664,10 @@
         <v>10</v>
       </c>
       <c r="D376" t="n">
-        <v>610.358333558047</v>
+        <v>2781.67239967945</v>
       </c>
       <c r="E376" t="n">
-        <v>593.366629653672</v>
+        <v>2666.24215844291</v>
       </c>
     </row>
     <row r="377">
@@ -6683,10 +6681,10 @@
         <v>10</v>
       </c>
       <c r="D377" t="n">
-        <v>608.893580993493</v>
+        <v>2805.26576985335</v>
       </c>
       <c r="E377" t="n">
-        <v>596.292982187191</v>
+        <v>2683.43007072986</v>
       </c>
     </row>
     <row r="378">
@@ -6700,7 +6698,7 @@
         <v>10</v>
       </c>
       <c r="D378" t="n">
-        <v>185.175378735673</v>
+        <v>669.26720825666</v>
       </c>
       <c r="E378"/>
     </row>
@@ -6715,7 +6713,7 @@
         <v>10</v>
       </c>
       <c r="D379" t="n">
-        <v>185.193975642367</v>
+        <v>664.958315536495</v>
       </c>
       <c r="E379"/>
     </row>
@@ -6730,7 +6728,7 @@
         <v>10</v>
       </c>
       <c r="D380" t="n">
-        <v>183.972416263821</v>
+        <v>656.846672308277</v>
       </c>
       <c r="E380"/>
     </row>
@@ -6745,7 +6743,7 @@
         <v>10</v>
       </c>
       <c r="D381" t="n">
-        <v>184.318393298999</v>
+        <v>643.027847390673</v>
       </c>
       <c r="E381"/>
     </row>
@@ -6760,7 +6758,7 @@
         <v>10</v>
       </c>
       <c r="D382" t="n">
-        <v>183.142154640085</v>
+        <v>632.879349111086</v>
       </c>
       <c r="E382"/>
     </row>
@@ -6775,7 +6773,7 @@
         <v>10</v>
       </c>
       <c r="D383" t="n">
-        <v>183.193088570506</v>
+        <v>634.627685029074</v>
       </c>
       <c r="E383"/>
     </row>
@@ -6790,7 +6788,7 @@
         <v>10</v>
       </c>
       <c r="D384" t="n">
-        <v>183.528198257356</v>
+        <v>628.465447667154</v>
       </c>
       <c r="E384"/>
     </row>
@@ -6805,7 +6803,7 @@
         <v>10</v>
       </c>
       <c r="D385" t="n">
-        <v>184.20570723131</v>
+        <v>625.772813746785</v>
       </c>
       <c r="E385"/>
     </row>
@@ -6820,7 +6818,7 @@
         <v>10</v>
       </c>
       <c r="D386" t="n">
-        <v>184.874308838098</v>
+        <v>629.148350899884</v>
       </c>
       <c r="E386"/>
     </row>
@@ -6835,7 +6833,7 @@
         <v>10</v>
       </c>
       <c r="D387" t="n">
-        <v>185.678267063642</v>
+        <v>617.665167867293</v>
       </c>
       <c r="E387"/>
     </row>
@@ -6850,7 +6848,7 @@
         <v>10</v>
       </c>
       <c r="D388" t="n">
-        <v>185.97671422764</v>
+        <v>619.465745003562</v>
       </c>
       <c r="E388"/>
     </row>
@@ -6865,10 +6863,10 @@
         <v>10</v>
       </c>
       <c r="D389" t="n">
-        <v>185.715794125331</v>
+        <v>615.078373670658</v>
       </c>
       <c r="E389" t="n">
-        <v>184.581199741236</v>
+        <v>636.433581373967</v>
       </c>
     </row>
     <row r="390">
@@ -6882,10 +6880,10 @@
         <v>10</v>
       </c>
       <c r="D390" t="n">
-        <v>186.458593583096</v>
+        <v>592.592436691143</v>
       </c>
       <c r="E390" t="n">
-        <v>184.688134311854</v>
+        <v>630.04401707684</v>
       </c>
     </row>
     <row r="391">
@@ -6899,10 +6897,10 @@
         <v>10</v>
       </c>
       <c r="D391" t="n">
-        <v>186.92420332653</v>
+        <v>580.698904733195</v>
       </c>
       <c r="E391" t="n">
-        <v>184.832319952201</v>
+        <v>623.022399509899</v>
       </c>
     </row>
     <row r="392">
@@ -6916,10 +6914,10 @@
         <v>10</v>
       </c>
       <c r="D392" t="n">
-        <v>186.570986440857</v>
+        <v>568.147479480282</v>
       </c>
       <c r="E392" t="n">
-        <v>185.048867466954</v>
+        <v>615.630800107566</v>
       </c>
     </row>
     <row r="393">
@@ -6933,10 +6931,10 @@
         <v>10</v>
       </c>
       <c r="D393" t="n">
-        <v>186.830719947381</v>
+        <v>550.344821564278</v>
       </c>
       <c r="E393" t="n">
-        <v>185.258228020986</v>
+        <v>607.907214622033</v>
       </c>
     </row>
     <row r="394">
@@ -6950,10 +6948,10 @@
         <v>10</v>
       </c>
       <c r="D394" t="n">
-        <v>187.388053551495</v>
+        <v>538.183980824089</v>
       </c>
       <c r="E394" t="n">
-        <v>185.61205293027</v>
+        <v>600.01593393145</v>
       </c>
     </row>
     <row r="395">
@@ -6967,10 +6965,10 @@
         <v>10</v>
       </c>
       <c r="D395" t="n">
-        <v>187.204113781375</v>
+        <v>531.865344590277</v>
       </c>
       <c r="E395" t="n">
-        <v>185.946305031176</v>
+        <v>591.45240556155</v>
       </c>
     </row>
     <row r="396">
@@ -6984,10 +6982,10 @@
         <v>10</v>
       </c>
       <c r="D396" t="n">
-        <v>186.234251378932</v>
+        <v>532.717437480102</v>
       </c>
       <c r="E396" t="n">
-        <v>186.171809457974</v>
+        <v>583.473404712629</v>
       </c>
     </row>
     <row r="397">
@@ -7001,10 +6999,10 @@
         <v>10</v>
       </c>
       <c r="D397" t="n">
-        <v>186.664783932602</v>
+        <v>535.859935588427</v>
       </c>
       <c r="E397" t="n">
-        <v>186.376732516415</v>
+        <v>575.980664866099</v>
       </c>
     </row>
     <row r="398">
@@ -7018,10 +7016,10 @@
         <v>10</v>
       </c>
       <c r="D398" t="n">
-        <v>186.580067822415</v>
+        <v>532.734967276674</v>
       </c>
       <c r="E398" t="n">
-        <v>186.518879098441</v>
+        <v>567.946216230832</v>
       </c>
     </row>
     <row r="399">
@@ -7035,10 +7033,10 @@
         <v>10</v>
       </c>
       <c r="D399" t="n">
-        <v>186.972572685176</v>
+        <v>528.286621587053</v>
       </c>
       <c r="E399" t="n">
-        <v>186.626737900236</v>
+        <v>560.498004040812</v>
       </c>
     </row>
     <row r="400">
@@ -7052,10 +7050,10 @@
         <v>10</v>
       </c>
       <c r="D400" t="n">
-        <v>187.231129311599</v>
+        <v>527.041870323965</v>
       </c>
       <c r="E400" t="n">
-        <v>186.731272490566</v>
+        <v>552.796014484179</v>
       </c>
     </row>
     <row r="401">
@@ -7069,10 +7067,10 @@
         <v>10</v>
       </c>
       <c r="D401" t="n">
-        <v>188.274032140304</v>
+        <v>519.75104907723</v>
       </c>
       <c r="E401" t="n">
-        <v>186.944458991813</v>
+        <v>544.85207076806</v>
       </c>
     </row>
     <row r="402">
@@ -7086,10 +7084,10 @@
         <v>10</v>
       </c>
       <c r="D402" t="n">
-        <v>187.248395169581</v>
+        <v>520.937185169896</v>
       </c>
       <c r="E402" t="n">
-        <v>187.010275790687</v>
+        <v>538.880799807956</v>
       </c>
     </row>
     <row r="403">
@@ -7103,10 +7101,10 @@
         <v>10</v>
       </c>
       <c r="D403" t="n">
-        <v>187.727778636139</v>
+        <v>522.268338215199</v>
       </c>
       <c r="E403" t="n">
-        <v>187.077240399821</v>
+        <v>534.011585931456</v>
       </c>
     </row>
     <row r="404">
@@ -7120,10 +7118,10 @@
         <v>10</v>
       </c>
       <c r="D404" t="n">
-        <v>188.081014260649</v>
+        <v>521.631449201455</v>
       </c>
       <c r="E404" t="n">
-        <v>187.203076051471</v>
+        <v>530.135250074887</v>
       </c>
     </row>
     <row r="405">
@@ -7137,10 +7135,10 @@
         <v>10</v>
       </c>
       <c r="D405" t="n">
-        <v>187.503210437951</v>
+        <v>517.172946716155</v>
       </c>
       <c r="E405" t="n">
-        <v>187.259116925685</v>
+        <v>527.370927170877</v>
       </c>
     </row>
     <row r="406">
@@ -7154,10 +7152,10 @@
         <v>10</v>
       </c>
       <c r="D406" t="n">
-        <v>188.199390609892</v>
+        <v>518.523992562075</v>
       </c>
       <c r="E406" t="n">
-        <v>187.326728347218</v>
+        <v>525.732594815709</v>
       </c>
     </row>
     <row r="407">
@@ -7171,10 +7169,10 @@
         <v>10</v>
       </c>
       <c r="D407" t="n">
-        <v>188.233638121479</v>
+        <v>529.179447283191</v>
       </c>
       <c r="E407" t="n">
-        <v>187.412522042226</v>
+        <v>525.508770040119</v>
       </c>
     </row>
     <row r="408">
@@ -7188,10 +7186,10 @@
         <v>10</v>
       </c>
       <c r="D408" t="n">
-        <v>188.83272276984</v>
+        <v>524.437407781749</v>
       </c>
       <c r="E408" t="n">
-        <v>187.629061324802</v>
+        <v>524.818767565256</v>
       </c>
     </row>
     <row r="409">
@@ -7205,10 +7203,10 @@
         <v>10</v>
       </c>
       <c r="D409" t="n">
-        <v>189.132257013427</v>
+        <v>530.894968229583</v>
       </c>
       <c r="E409" t="n">
-        <v>187.834684081538</v>
+        <v>524.405020285352</v>
       </c>
     </row>
     <row r="410">
@@ -7222,10 +7220,10 @@
         <v>10</v>
       </c>
       <c r="D410" t="n">
-        <v>189.393894215159</v>
+        <v>528.264316071989</v>
       </c>
       <c r="E410" t="n">
-        <v>188.069169614266</v>
+        <v>524.032466018295</v>
       </c>
     </row>
     <row r="411">
@@ -7239,10 +7237,10 @@
         <v>10</v>
       </c>
       <c r="D411" t="n">
-        <v>189.885826478381</v>
+        <v>530.098819528805</v>
       </c>
       <c r="E411" t="n">
-        <v>188.3119407637</v>
+        <v>524.183482513441</v>
       </c>
     </row>
     <row r="412">
@@ -7256,10 +7254,10 @@
         <v>10</v>
       </c>
       <c r="D412" t="n">
-        <v>190.725295461813</v>
+        <v>531.264518772013</v>
       </c>
       <c r="E412" t="n">
-        <v>188.603121276218</v>
+        <v>524.535369884112</v>
       </c>
     </row>
     <row r="413">
@@ -7273,10 +7271,10 @@
         <v>10</v>
       </c>
       <c r="D413" t="n">
-        <v>188.960366033895</v>
+        <v>536.20069633963</v>
       </c>
       <c r="E413" t="n">
-        <v>188.660315767351</v>
+        <v>525.906173822645</v>
       </c>
     </row>
     <row r="414">
@@ -7290,10 +7288,10 @@
         <v>10</v>
       </c>
       <c r="D414" t="n">
-        <v>190.151165417206</v>
+        <v>535.358296543351</v>
       </c>
       <c r="E414" t="n">
-        <v>188.902213287986</v>
+        <v>527.107933103766</v>
       </c>
     </row>
     <row r="415">
@@ -7307,10 +7305,10 @@
         <v>10</v>
       </c>
       <c r="D415" t="n">
-        <v>189.816478597326</v>
+        <v>537.520117728456</v>
       </c>
       <c r="E415" t="n">
-        <v>189.076271618085</v>
+        <v>528.378914729871</v>
       </c>
     </row>
     <row r="416">
@@ -7324,10 +7322,10 @@
         <v>10</v>
       </c>
       <c r="D416" t="n">
-        <v>190.199631962079</v>
+        <v>544.290646174233</v>
       </c>
       <c r="E416" t="n">
-        <v>189.252823093204</v>
+        <v>530.267181144269</v>
       </c>
     </row>
     <row r="417">
@@ -7341,10 +7339,10 @@
         <v>10</v>
       </c>
       <c r="D417" t="n">
-        <v>190.441668402092</v>
+        <v>542.620339420748</v>
       </c>
       <c r="E417" t="n">
-        <v>189.497694590216</v>
+        <v>532.387797202985</v>
       </c>
     </row>
     <row r="418">
@@ -7358,10 +7356,10 @@
         <v>10</v>
       </c>
       <c r="D418" t="n">
-        <v>190.324754301917</v>
+        <v>538.144132262496</v>
       </c>
       <c r="E418" t="n">
-        <v>189.674808231218</v>
+        <v>534.022808844687</v>
       </c>
     </row>
     <row r="419">
@@ -7375,10 +7373,10 @@
         <v>10</v>
       </c>
       <c r="D419" t="n">
-        <v>190.251505147262</v>
+        <v>546.172486614165</v>
       </c>
       <c r="E419" t="n">
-        <v>189.8429638167</v>
+        <v>535.438895455601</v>
       </c>
     </row>
     <row r="420">
@@ -7392,10 +7390,10 @@
         <v>10</v>
       </c>
       <c r="D420" t="n">
-        <v>190.666040589838</v>
+        <v>536.949505622859</v>
       </c>
       <c r="E420" t="n">
-        <v>189.9957403017</v>
+        <v>536.481570275694</v>
       </c>
     </row>
     <row r="421">
@@ -7409,10 +7407,10 @@
         <v>10</v>
       </c>
       <c r="D421" t="n">
-        <v>201.031192245008</v>
+        <v>545.042537839482</v>
       </c>
       <c r="E421" t="n">
-        <v>190.987318237665</v>
+        <v>537.660534409852</v>
       </c>
     </row>
     <row r="422">
@@ -7426,10 +7424,10 @@
         <v>10</v>
       </c>
       <c r="D422" t="n">
-        <v>202.370883868409</v>
+        <v>535.748961532829</v>
       </c>
       <c r="E422" t="n">
-        <v>192.068734042102</v>
+        <v>538.284254864922</v>
       </c>
     </row>
     <row r="423">
@@ -7443,10 +7441,10 @@
         <v>10</v>
       </c>
       <c r="D423" t="n">
-        <v>202.646816929416</v>
+        <v>537.57802256554</v>
       </c>
       <c r="E423" t="n">
-        <v>193.132149913022</v>
+        <v>538.90752178465</v>
       </c>
     </row>
     <row r="424">
@@ -7460,10 +7458,10 @@
         <v>10</v>
       </c>
       <c r="D424" t="n">
-        <v>192.400405803348</v>
+        <v>536.732967670616</v>
       </c>
       <c r="E424" t="n">
-        <v>193.271742441483</v>
+        <v>539.363225859534</v>
       </c>
     </row>
     <row r="425">
@@ -7477,10 +7475,10 @@
         <v>10</v>
       </c>
       <c r="D425" t="n">
-        <v>192.470986492932</v>
+        <v>541.273792539344</v>
       </c>
       <c r="E425" t="n">
-        <v>193.564294146403</v>
+        <v>539.785983876177</v>
       </c>
     </row>
     <row r="426">
@@ -7494,10 +7492,10 @@
         <v>10</v>
       </c>
       <c r="D426" t="n">
-        <v>193.017937227755</v>
+        <v>547.106766250921</v>
       </c>
       <c r="E426" t="n">
-        <v>193.803191797282</v>
+        <v>540.765023018474</v>
       </c>
     </row>
     <row r="427">
@@ -7511,10 +7509,10 @@
         <v>10</v>
       </c>
       <c r="D427" t="n">
-        <v>193.796429945677</v>
+        <v>555.814445290349</v>
       </c>
       <c r="E427" t="n">
-        <v>194.134854409644</v>
+        <v>542.289550315298</v>
       </c>
     </row>
     <row r="428">
@@ -7528,10 +7526,10 @@
         <v>10</v>
       </c>
       <c r="D428" t="n">
-        <v>193.978910908151</v>
+        <v>551.819170429537</v>
       </c>
       <c r="E428" t="n">
-        <v>194.449794321817</v>
+        <v>542.916927336574</v>
       </c>
     </row>
     <row r="429">
@@ -7545,10 +7543,10 @@
         <v>10</v>
       </c>
       <c r="D429" t="n">
-        <v>194.51293421091</v>
+        <v>554.665865449073</v>
       </c>
       <c r="E429" t="n">
-        <v>194.789066472552</v>
+        <v>543.920721172268</v>
       </c>
     </row>
     <row r="430">
@@ -7562,10 +7560,10 @@
         <v>10</v>
       </c>
       <c r="D430" t="n">
-        <v>194.77393889754</v>
+        <v>554.59480160994</v>
       </c>
       <c r="E430" t="n">
-        <v>195.15983185552</v>
+        <v>545.291610284555</v>
       </c>
     </row>
     <row r="431">
@@ -7579,10 +7577,10 @@
         <v>10</v>
       </c>
       <c r="D431" t="n">
-        <v>205.921558411793</v>
+        <v>542.332984042469</v>
       </c>
       <c r="E431" t="n">
-        <v>196.465669627565</v>
+        <v>544.971651736913</v>
       </c>
     </row>
     <row r="432">
@@ -7596,10 +7594,10 @@
         <v>10</v>
       </c>
       <c r="D432" t="n">
-        <v>199.691186633271</v>
+        <v>549.172899110822</v>
       </c>
       <c r="E432" t="n">
-        <v>197.217765131184</v>
+        <v>545.99026786091</v>
       </c>
     </row>
     <row r="433">
@@ -7613,10 +7611,10 @@
         <v>10</v>
       </c>
       <c r="D433" t="n">
-        <v>200.256343529109</v>
+        <v>553.584642426177</v>
       </c>
       <c r="E433" t="n">
-        <v>197.153194404859</v>
+        <v>546.702109909801</v>
       </c>
     </row>
     <row r="434">
@@ -7630,10 +7628,10 @@
         <v>10</v>
       </c>
       <c r="D434" t="n">
-        <v>196.91191666621</v>
+        <v>554.339198922059</v>
       </c>
       <c r="E434" t="n">
-        <v>196.698280471343</v>
+        <v>548.251296358904</v>
       </c>
     </row>
     <row r="435">
@@ -7647,10 +7645,10 @@
         <v>10</v>
       </c>
       <c r="D435" t="n">
-        <v>196.938095369426</v>
+        <v>556.959435082801</v>
       </c>
       <c r="E435" t="n">
-        <v>196.222553674677</v>
+        <v>549.866414068676</v>
       </c>
     </row>
     <row r="436">
@@ -7664,10 +7662,10 @@
         <v>10</v>
       </c>
       <c r="D436" t="n">
-        <v>196.978710856876</v>
+        <v>566.172994095383</v>
       </c>
       <c r="E436" t="n">
-        <v>196.604079095804</v>
+        <v>552.319749604073</v>
       </c>
     </row>
     <row r="437">
@@ -7681,10 +7679,10 @@
         <v>10</v>
       </c>
       <c r="D437" t="n">
-        <v>195.627899547841</v>
+        <v>561.149331399098</v>
       </c>
       <c r="E437" t="n">
-        <v>196.867155183713</v>
+        <v>553.976044509052</v>
       </c>
     </row>
     <row r="438">
@@ -7698,10 +7696,10 @@
         <v>10</v>
       </c>
       <c r="D438" t="n">
-        <v>197.309706431249</v>
+        <v>550.800175865204</v>
       </c>
       <c r="E438" t="n">
-        <v>197.224802617338</v>
+        <v>554.283828643576</v>
       </c>
     </row>
     <row r="439">
@@ -7715,10 +7713,10 @@
         <v>10</v>
       </c>
       <c r="D439" t="n">
-        <v>197.480799110427</v>
+        <v>566.282634402842</v>
       </c>
       <c r="E439" t="n">
-        <v>197.531833381067</v>
+        <v>555.156177736284</v>
       </c>
     </row>
     <row r="440">
@@ -7732,10 +7730,10 @@
         <v>10</v>
       </c>
       <c r="D440" t="n">
-        <v>197.872471542118</v>
+        <v>573.038567362652</v>
       </c>
       <c r="E440" t="n">
-        <v>197.856296767231</v>
+        <v>556.924460814043</v>
       </c>
     </row>
     <row r="441">
@@ -7749,10 +7747,10 @@
         <v>10</v>
       </c>
       <c r="D441" t="n">
-        <v>198.56232602862</v>
+        <v>573.777350591274</v>
       </c>
       <c r="E441" t="n">
-        <v>198.193746085373</v>
+        <v>558.517084575893</v>
       </c>
     </row>
     <row r="442">
@@ -7766,10 +7764,10 @@
         <v>10</v>
       </c>
       <c r="D442" t="n">
-        <v>197.937811250727</v>
+        <v>576.220295412062</v>
       </c>
       <c r="E442" t="n">
-        <v>198.457402114806</v>
+        <v>560.319209059404</v>
       </c>
     </row>
     <row r="443">
@@ -7783,10 +7781,10 @@
         <v>10</v>
       </c>
       <c r="D443" t="n">
-        <v>197.760705250066</v>
+        <v>592.288917948193</v>
       </c>
       <c r="E443" t="n">
-        <v>197.777331017995</v>
+        <v>564.482203551547</v>
       </c>
     </row>
     <row r="444">
@@ -7800,10 +7798,10 @@
         <v>10</v>
       </c>
       <c r="D444" t="n">
-        <v>197.823635345658</v>
+        <v>586.516807615162</v>
       </c>
       <c r="E444" t="n">
-        <v>197.621701744027</v>
+        <v>567.594195926909</v>
       </c>
     </row>
     <row r="445">
@@ -7817,10 +7815,10 @@
         <v>10</v>
       </c>
       <c r="D445" t="n">
-        <v>198.158291790696</v>
+        <v>594.460199885595</v>
       </c>
       <c r="E445" t="n">
-        <v>197.44686409916</v>
+        <v>571.00049238186</v>
       </c>
     </row>
     <row r="446">
@@ -7834,10 +7832,10 @@
         <v>10</v>
       </c>
       <c r="D446" t="n">
-        <v>198.623663040932</v>
+        <v>596.341532295771</v>
       </c>
       <c r="E446" t="n">
-        <v>197.589509630386</v>
+        <v>574.50068682967</v>
       </c>
     </row>
     <row r="447">
@@ -7851,10 +7849,10 @@
         <v>10</v>
       </c>
       <c r="D447" t="n">
-        <v>198.9601608028</v>
+        <v>601.387165180222</v>
       </c>
       <c r="E447" t="n">
-        <v>197.758015083168</v>
+        <v>578.202997671121</v>
       </c>
     </row>
     <row r="448">
@@ -7868,10 +7866,10 @@
         <v>10</v>
       </c>
       <c r="D448" t="n">
-        <v>198.194328122039</v>
+        <v>602.491217667505</v>
       </c>
       <c r="E448" t="n">
-        <v>197.859316521931</v>
+        <v>581.229516302132</v>
       </c>
     </row>
     <row r="449">
@@ -7885,10 +7883,10 @@
         <v>10</v>
       </c>
       <c r="D449" t="n">
-        <v>198.280282462736</v>
+        <v>594.33533985414</v>
       </c>
       <c r="E449" t="n">
-        <v>198.080348431506</v>
+        <v>583.995017006719</v>
       </c>
     </row>
     <row r="450">
@@ -7902,10 +7900,10 @@
         <v>10</v>
       </c>
       <c r="D450" t="n">
-        <v>198.831414692704</v>
+        <v>587.877189178223</v>
       </c>
       <c r="E450" t="n">
-        <v>198.207157453294</v>
+        <v>587.084768116137</v>
       </c>
     </row>
     <row r="451">
@@ -7919,10 +7917,10 @@
         <v>10</v>
       </c>
       <c r="D451" t="n">
-        <v>199.468069183848</v>
+        <v>604.345206657874</v>
       </c>
       <c r="E451" t="n">
-        <v>198.372763292745</v>
+        <v>590.256649137389</v>
       </c>
     </row>
     <row r="452">
@@ -7936,10 +7934,10 @@
         <v>10</v>
       </c>
       <c r="D452" t="n">
-        <v>200.105263099909</v>
+        <v>610.358333558047</v>
       </c>
       <c r="E452" t="n">
-        <v>198.558829255895</v>
+        <v>593.366629653672</v>
       </c>
     </row>
     <row r="453">
@@ -7953,10 +7951,10 @@
         <v>10</v>
       </c>
       <c r="D453" t="n">
-        <v>199.900668796946</v>
+        <v>608.893580993493</v>
       </c>
       <c r="E453" t="n">
-        <v>198.670357819922</v>
+        <v>596.292982187191</v>
       </c>
     </row>
     <row r="454">
@@ -7970,7 +7968,7 @@
         <v>10</v>
       </c>
       <c r="D454" t="n">
-        <v>64.0491020677844</v>
+        <v>185.175378735673</v>
       </c>
       <c r="E454"/>
     </row>
@@ -7985,7 +7983,7 @@
         <v>10</v>
       </c>
       <c r="D455" t="n">
-        <v>61.82443611649</v>
+        <v>185.193975642367</v>
       </c>
       <c r="E455"/>
     </row>
@@ -8000,7 +7998,7 @@
         <v>10</v>
       </c>
       <c r="D456" t="n">
-        <v>60.6352266062756</v>
+        <v>183.972416263821</v>
       </c>
       <c r="E456"/>
     </row>
@@ -8015,7 +8013,7 @@
         <v>10</v>
       </c>
       <c r="D457" t="n">
-        <v>61.4159956467082</v>
+        <v>184.318393298999</v>
       </c>
       <c r="E457"/>
     </row>
@@ -8030,7 +8028,7 @@
         <v>10</v>
       </c>
       <c r="D458" t="n">
-        <v>58.9799837712983</v>
+        <v>183.142154640085</v>
       </c>
       <c r="E458"/>
     </row>
@@ -8045,7 +8043,7 @@
         <v>10</v>
       </c>
       <c r="D459" t="n">
-        <v>56.2904113042008</v>
+        <v>183.193088570506</v>
       </c>
       <c r="E459"/>
     </row>
@@ -8060,7 +8058,7 @@
         <v>10</v>
       </c>
       <c r="D460" t="n">
-        <v>53.8016850191522</v>
+        <v>183.528198257356</v>
       </c>
       <c r="E460"/>
     </row>
@@ -8075,7 +8073,7 @@
         <v>10</v>
       </c>
       <c r="D461" t="n">
-        <v>55.1402706172024</v>
+        <v>184.20570723131</v>
       </c>
       <c r="E461"/>
     </row>
@@ -8090,7 +8088,7 @@
         <v>10</v>
       </c>
       <c r="D462" t="n">
-        <v>54.0339910631902</v>
+        <v>184.874308838098</v>
       </c>
       <c r="E462"/>
     </row>
@@ -8105,7 +8103,7 @@
         <v>10</v>
       </c>
       <c r="D463" t="n">
-        <v>48.5741641237493</v>
+        <v>185.678267063642</v>
       </c>
       <c r="E463"/>
     </row>
@@ -8120,7 +8118,7 @@
         <v>10</v>
       </c>
       <c r="D464" t="n">
-        <v>46.9947674627455</v>
+        <v>185.97671422764</v>
       </c>
       <c r="E464"/>
     </row>
@@ -8135,10 +8133,10 @@
         <v>10</v>
       </c>
       <c r="D465" t="n">
-        <v>44.596413565117</v>
+        <v>185.715794125331</v>
       </c>
       <c r="E465" t="n">
-        <v>55.5280372803262</v>
+        <v>184.581199741236</v>
       </c>
     </row>
     <row r="466">
@@ -8152,10 +8150,10 @@
         <v>10</v>
       </c>
       <c r="D466" t="n">
-        <v>45.8658461859098</v>
+        <v>186.458593583096</v>
       </c>
       <c r="E466" t="n">
-        <v>54.0127659568366</v>
+        <v>184.688134311854</v>
       </c>
     </row>
     <row r="467">
@@ -8169,10 +8167,10 @@
         <v>10</v>
       </c>
       <c r="D467" t="n">
-        <v>45.1959267736983</v>
+        <v>186.92420332653</v>
       </c>
       <c r="E467" t="n">
-        <v>52.6270568449373</v>
+        <v>184.832319952201</v>
       </c>
     </row>
     <row r="468">
@@ -8186,10 +8184,10 @@
         <v>10</v>
       </c>
       <c r="D468" t="n">
-        <v>45.6485285739431</v>
+        <v>186.570986440857</v>
       </c>
       <c r="E468" t="n">
-        <v>51.3781653422429</v>
+        <v>185.048867466954</v>
       </c>
     </row>
     <row r="469">
@@ -8203,10 +8201,10 @@
         <v>10</v>
       </c>
       <c r="D469" t="n">
-        <v>45.0888245569265</v>
+        <v>186.830719947381</v>
       </c>
       <c r="E469" t="n">
-        <v>50.0175677514278</v>
+        <v>185.258228020986</v>
       </c>
     </row>
     <row r="470">
@@ -8220,10 +8218,10 @@
         <v>10</v>
       </c>
       <c r="D470" t="n">
-        <v>44.9757110666744</v>
+        <v>187.388053551495</v>
       </c>
       <c r="E470" t="n">
-        <v>48.8505450260425</v>
+        <v>185.61205293027</v>
       </c>
     </row>
     <row r="471">
@@ -8237,10 +8235,10 @@
         <v>10</v>
       </c>
       <c r="D471" t="n">
-        <v>42.9290498798745</v>
+        <v>187.204113781375</v>
       </c>
       <c r="E471" t="n">
-        <v>47.7370982406819</v>
+        <v>185.946305031176</v>
       </c>
     </row>
     <row r="472">
@@ -8254,10 +8252,10 @@
         <v>10</v>
       </c>
       <c r="D472" t="n">
-        <v>42.0737622407422</v>
+        <v>186.234251378932</v>
       </c>
       <c r="E472" t="n">
-        <v>46.7597713424811</v>
+        <v>186.171809457974</v>
       </c>
     </row>
     <row r="473">
@@ -8271,10 +8269,10 @@
         <v>10</v>
       </c>
       <c r="D473" t="n">
-        <v>43.8942130794083</v>
+        <v>186.664783932602</v>
       </c>
       <c r="E473" t="n">
-        <v>45.8225998809983</v>
+        <v>186.376732516415</v>
       </c>
     </row>
     <row r="474">
@@ -8288,10 +8286,10 @@
         <v>10</v>
       </c>
       <c r="D474" t="n">
-        <v>43.4821484486287</v>
+        <v>186.580067822415</v>
       </c>
       <c r="E474" t="n">
-        <v>44.9432796631181</v>
+        <v>186.518879098441</v>
       </c>
     </row>
     <row r="475">
@@ -8305,10 +8303,10 @@
         <v>10</v>
       </c>
       <c r="D475" t="n">
-        <v>43.840548493883</v>
+        <v>186.972572685176</v>
       </c>
       <c r="E475" t="n">
-        <v>44.5488116939626</v>
+        <v>186.626737900236</v>
       </c>
     </row>
     <row r="476">
@@ -8322,10 +8320,10 @@
         <v>10</v>
       </c>
       <c r="D476" t="n">
-        <v>43.890692946002</v>
+        <v>187.231129311599</v>
       </c>
       <c r="E476" t="n">
-        <v>44.2901388175673</v>
+        <v>186.731272490566</v>
       </c>
     </row>
     <row r="477">
@@ -8339,10 +8337,10 @@
         <v>10</v>
       </c>
       <c r="D477" t="n">
-        <v>45.9908264862381</v>
+        <v>188.274032140304</v>
       </c>
       <c r="E477" t="n">
-        <v>44.4063398943274</v>
+        <v>186.944458991813</v>
       </c>
     </row>
     <row r="478">
@@ -8356,10 +8354,10 @@
         <v>10</v>
       </c>
       <c r="D478" t="n">
-        <v>43.0178676559709</v>
+        <v>187.248395169581</v>
       </c>
       <c r="E478" t="n">
-        <v>44.1690083501658</v>
+        <v>187.010275790687</v>
       </c>
     </row>
     <row r="479">
@@ -8373,10 +8371,10 @@
         <v>10</v>
       </c>
       <c r="D479" t="n">
-        <v>45.8257259880181</v>
+        <v>187.727778636139</v>
       </c>
       <c r="E479" t="n">
-        <v>44.2214916180258</v>
+        <v>187.077240399821</v>
       </c>
     </row>
     <row r="480">
@@ -8390,10 +8388,10 @@
         <v>10</v>
       </c>
       <c r="D480" t="n">
-        <v>45.7049284455735</v>
+        <v>188.081014260649</v>
       </c>
       <c r="E480" t="n">
-        <v>44.2261916073284</v>
+        <v>187.203076051471</v>
       </c>
     </row>
     <row r="481">
@@ -8407,10 +8405,10 @@
         <v>10</v>
       </c>
       <c r="D481" t="n">
-        <v>45.4813284829068</v>
+        <v>187.503210437951</v>
       </c>
       <c r="E481" t="n">
-        <v>44.2589002678267</v>
+        <v>187.259116925685</v>
       </c>
     </row>
     <row r="482">
@@ -8424,10 +8422,10 @@
         <v>10</v>
       </c>
       <c r="D482" t="n">
-        <v>46.584096899323</v>
+        <v>188.199390609892</v>
       </c>
       <c r="E482" t="n">
-        <v>44.3929324205474</v>
+        <v>187.326728347218</v>
       </c>
     </row>
     <row r="483">
@@ -8441,10 +8439,10 @@
         <v>10</v>
       </c>
       <c r="D483" t="n">
-        <v>47.0840412931037</v>
+        <v>188.233638121479</v>
       </c>
       <c r="E483" t="n">
-        <v>44.7391817049832</v>
+        <v>187.412522042227</v>
       </c>
     </row>
     <row r="484">
@@ -8458,10 +8456,10 @@
         <v>10</v>
       </c>
       <c r="D484" t="n">
-        <v>47.1245762632958</v>
+        <v>188.83272276984</v>
       </c>
       <c r="E484" t="n">
-        <v>45.1600828735293</v>
+        <v>187.629061324802</v>
       </c>
     </row>
     <row r="485">
@@ -8475,10 +8473,10 @@
         <v>10</v>
       </c>
       <c r="D485" t="n">
-        <v>47.4451526704188</v>
+        <v>189.132257013427</v>
       </c>
       <c r="E485" t="n">
-        <v>45.4559945061135</v>
+        <v>187.834684081538</v>
       </c>
     </row>
     <row r="486">
@@ -8492,10 +8490,10 @@
         <v>10</v>
       </c>
       <c r="D486" t="n">
-        <v>47.1436184701266</v>
+        <v>189.393894215159</v>
       </c>
       <c r="E486" t="n">
-        <v>45.761117007905</v>
+        <v>188.069169614266</v>
       </c>
     </row>
     <row r="487">
@@ -8509,10 +8507,10 @@
         <v>10</v>
       </c>
       <c r="D487" t="n">
-        <v>48.2469082598945</v>
+        <v>189.885826478381</v>
       </c>
       <c r="E487" t="n">
-        <v>46.1283136550726</v>
+        <v>188.3119407637</v>
       </c>
     </row>
     <row r="488">
@@ -8526,10 +8524,10 @@
         <v>10</v>
       </c>
       <c r="D488" t="n">
-        <v>49.6306163820841</v>
+        <v>190.725295461813</v>
       </c>
       <c r="E488" t="n">
-        <v>46.6066406080795</v>
+        <v>188.603121276218</v>
       </c>
     </row>
     <row r="489">
@@ -8543,10 +8541,10 @@
         <v>10</v>
       </c>
       <c r="D489" t="n">
-        <v>52.3959774066045</v>
+        <v>188.960366033895</v>
       </c>
       <c r="E489" t="n">
-        <v>47.1404031847767</v>
+        <v>188.660315767351</v>
       </c>
     </row>
     <row r="490">
@@ -8560,10 +8558,10 @@
         <v>10</v>
       </c>
       <c r="D490" t="n">
-        <v>50.1677625656606</v>
+        <v>190.151165417206</v>
       </c>
       <c r="E490" t="n">
-        <v>47.7362277605842</v>
+        <v>188.902213287986</v>
       </c>
     </row>
     <row r="491">
@@ -8577,10 +8575,10 @@
         <v>10</v>
       </c>
       <c r="D491" t="n">
-        <v>54.0515156251754</v>
+        <v>189.816478597326</v>
       </c>
       <c r="E491" t="n">
-        <v>48.4217102303473</v>
+        <v>189.076271618085</v>
       </c>
     </row>
     <row r="492">
@@ -8594,10 +8592,10 @@
         <v>10</v>
       </c>
       <c r="D492" t="n">
-        <v>55.6102871040039</v>
+        <v>190.199631962079</v>
       </c>
       <c r="E492" t="n">
-        <v>49.2471567852165</v>
+        <v>189.252823093204</v>
       </c>
     </row>
     <row r="493">
@@ -8611,10 +8609,10 @@
         <v>10</v>
       </c>
       <c r="D493" t="n">
-        <v>56.080347683551</v>
+        <v>190.441668402092</v>
       </c>
       <c r="E493" t="n">
-        <v>50.1304083852702</v>
+        <v>189.497694590216</v>
       </c>
     </row>
     <row r="494">
@@ -8628,10 +8626,10 @@
         <v>10</v>
       </c>
       <c r="D494" t="n">
-        <v>56.7503238301069</v>
+        <v>190.324754301917</v>
       </c>
       <c r="E494" t="n">
-        <v>50.9775939628355</v>
+        <v>189.674808231218</v>
       </c>
     </row>
     <row r="495">
@@ -8645,10 +8643,10 @@
         <v>10</v>
       </c>
       <c r="D495" t="n">
-        <v>55.3149417994787</v>
+        <v>190.251505147262</v>
       </c>
       <c r="E495" t="n">
-        <v>51.6635023383667</v>
+        <v>189.8429638167</v>
       </c>
     </row>
     <row r="496">
@@ -8662,10 +8660,10 @@
         <v>10</v>
       </c>
       <c r="D496" t="n">
-        <v>57.3015962094963</v>
+        <v>190.666040589838</v>
       </c>
       <c r="E496" t="n">
-        <v>52.5115873338834</v>
+        <v>189.9957403017</v>
       </c>
     </row>
     <row r="497">
@@ -8679,10 +8677,10 @@
         <v>10</v>
       </c>
       <c r="D497" t="n">
-        <v>55.839796755695</v>
+        <v>201.031192245008</v>
       </c>
       <c r="E497" t="n">
-        <v>53.2111410076565</v>
+        <v>190.987318237665</v>
       </c>
     </row>
     <row r="498">
@@ -8696,10 +8694,10 @@
         <v>10</v>
       </c>
       <c r="D498" t="n">
-        <v>58.4100577529056</v>
+        <v>202.370883868409</v>
       </c>
       <c r="E498" t="n">
-        <v>54.150010947888</v>
+        <v>192.068734042102</v>
       </c>
     </row>
     <row r="499">
@@ -8713,10 +8711,10 @@
         <v>10</v>
       </c>
       <c r="D499" t="n">
-        <v>61.459102509436</v>
+        <v>202.646816929416</v>
       </c>
       <c r="E499" t="n">
-        <v>55.2510271353498</v>
+        <v>193.132149913022</v>
       </c>
     </row>
     <row r="500">
@@ -8730,10 +8728,10 @@
         <v>10</v>
       </c>
       <c r="D500" t="n">
-        <v>63.1555939290306</v>
+        <v>192.400405803348</v>
       </c>
       <c r="E500" t="n">
-        <v>56.3781085975954</v>
+        <v>193.271742441483</v>
       </c>
     </row>
     <row r="501">
@@ -8747,10 +8745,10 @@
         <v>10</v>
       </c>
       <c r="D501" t="n">
-        <v>59.9914693942271</v>
+        <v>192.470986492932</v>
       </c>
       <c r="E501" t="n">
-        <v>57.0110662632306</v>
+        <v>193.564294146403</v>
       </c>
     </row>
     <row r="502">
@@ -8764,10 +8762,10 @@
         <v>10</v>
       </c>
       <c r="D502" t="n">
-        <v>57.8498393344469</v>
+        <v>193.017937227755</v>
       </c>
       <c r="E502" t="n">
-        <v>57.6512393272961</v>
+        <v>193.803191797282</v>
       </c>
     </row>
     <row r="503">
@@ -8781,10 +8779,10 @@
         <v>10</v>
       </c>
       <c r="D503" t="n">
-        <v>56.8784070481634</v>
+        <v>193.796429945677</v>
       </c>
       <c r="E503" t="n">
-        <v>57.8868136125451</v>
+        <v>194.134854409644</v>
       </c>
     </row>
     <row r="504">
@@ -8798,10 +8796,10 @@
         <v>10</v>
       </c>
       <c r="D504" t="n">
-        <v>56.364232487318</v>
+        <v>193.978910908151</v>
       </c>
       <c r="E504" t="n">
-        <v>57.949642394488</v>
+        <v>194.449794321817</v>
       </c>
     </row>
     <row r="505">
@@ -8815,10 +8813,10 @@
         <v>10</v>
       </c>
       <c r="D505" t="n">
-        <v>60.5983814579239</v>
+        <v>194.51293421091</v>
       </c>
       <c r="E505" t="n">
-        <v>58.326145209019</v>
+        <v>194.789066472552</v>
       </c>
     </row>
     <row r="506">
@@ -8832,10 +8830,10 @@
         <v>10</v>
       </c>
       <c r="D506" t="n">
-        <v>62.9413452381541</v>
+        <v>194.77393889754</v>
       </c>
       <c r="E506" t="n">
-        <v>58.8420636596896</v>
+        <v>195.159831855521</v>
       </c>
     </row>
     <row r="507">
@@ -8849,10 +8847,10 @@
         <v>10</v>
       </c>
       <c r="D507" t="n">
-        <v>61.0691303286673</v>
+        <v>205.921558411793</v>
       </c>
       <c r="E507" t="n">
-        <v>59.3215793704554</v>
+        <v>196.465669627565</v>
       </c>
     </row>
     <row r="508">
@@ -8866,10 +8864,10 @@
         <v>10</v>
       </c>
       <c r="D508" t="n">
-        <v>61.1007013020983</v>
+        <v>199.691186633271</v>
       </c>
       <c r="E508" t="n">
-        <v>59.6381714615055</v>
+        <v>197.217765131184</v>
       </c>
     </row>
     <row r="509">
@@ -8883,10 +8881,10 @@
         <v>10</v>
       </c>
       <c r="D509" t="n">
-        <v>64.1746175176083</v>
+        <v>200.256343529109</v>
       </c>
       <c r="E509" t="n">
-        <v>60.3327398583316</v>
+        <v>197.153194404859</v>
       </c>
     </row>
     <row r="510">
@@ -8900,10 +8898,10 @@
         <v>10</v>
       </c>
       <c r="D510" t="n">
-        <v>62.1350330436377</v>
+        <v>196.91191666621</v>
       </c>
       <c r="E510" t="n">
-        <v>60.6431544658926</v>
+        <v>196.698280471343</v>
       </c>
     </row>
     <row r="511">
@@ -8917,10 +8915,10 @@
         <v>10</v>
       </c>
       <c r="D511" t="n">
-        <v>63.8353624647531</v>
+        <v>196.938095369426</v>
       </c>
       <c r="E511" t="n">
-        <v>60.8411761288357</v>
+        <v>196.222553674677</v>
       </c>
     </row>
     <row r="512">
@@ -8934,10 +8932,10 @@
         <v>10</v>
       </c>
       <c r="D512" t="n">
-        <v>64.0081462744648</v>
+        <v>196.978710856876</v>
       </c>
       <c r="E512" t="n">
-        <v>60.9122221576219</v>
+        <v>196.604079095804</v>
       </c>
     </row>
     <row r="513">
@@ -8951,10 +8949,10 @@
         <v>10</v>
       </c>
       <c r="D513" t="n">
-        <v>63.7940916904896</v>
+        <v>195.627899547841</v>
       </c>
       <c r="E513" t="n">
-        <v>61.2291073489771</v>
+        <v>196.867155183713</v>
       </c>
     </row>
     <row r="514">
@@ -8968,10 +8966,10 @@
         <v>10</v>
       </c>
       <c r="D514" t="n">
-        <v>65.3221805257711</v>
+        <v>197.309706431249</v>
       </c>
       <c r="E514" t="n">
-        <v>61.8518024482541</v>
+        <v>197.224802617338</v>
       </c>
     </row>
     <row r="515">
@@ -8985,10 +8983,10 @@
         <v>10</v>
       </c>
       <c r="D515" t="n">
-        <v>65.4322028773246</v>
+        <v>197.480799110427</v>
       </c>
       <c r="E515" t="n">
-        <v>62.5646187673509</v>
+        <v>197.531833381067</v>
       </c>
     </row>
     <row r="516">
@@ -9002,10 +9000,10 @@
         <v>10</v>
       </c>
       <c r="D516" t="n">
-        <v>68.1999215365208</v>
+        <v>197.872471542118</v>
       </c>
       <c r="E516" t="n">
-        <v>63.5509261881178</v>
+        <v>197.856296767231</v>
       </c>
     </row>
     <row r="517">
@@ -9019,10 +9017,10 @@
         <v>10</v>
       </c>
       <c r="D517" t="n">
-        <v>68.1950801855598</v>
+        <v>198.56232602862</v>
       </c>
       <c r="E517" t="n">
-        <v>64.1839844154208</v>
+        <v>198.193746085373</v>
       </c>
     </row>
     <row r="518">
@@ -9036,10 +9034,10 @@
         <v>10</v>
       </c>
       <c r="D518" t="n">
-        <v>68.5149821612973</v>
+        <v>197.937811250727</v>
       </c>
       <c r="E518" t="n">
-        <v>64.6484541590161</v>
+        <v>198.457402114806</v>
       </c>
     </row>
     <row r="519">
@@ -9053,10 +9051,10 @@
         <v>10</v>
       </c>
       <c r="D519" t="n">
-        <v>68.437945654661</v>
+        <v>197.760705250066</v>
       </c>
       <c r="E519" t="n">
-        <v>65.2625221028489</v>
+        <v>197.777331017995</v>
       </c>
     </row>
     <row r="520">
@@ -9070,10 +9068,10 @@
         <v>10</v>
       </c>
       <c r="D520" t="n">
-        <v>72.3363188071854</v>
+        <v>197.823635345658</v>
       </c>
       <c r="E520" t="n">
-        <v>66.1988235616061</v>
+        <v>197.621701744027</v>
       </c>
     </row>
     <row r="521">
@@ -9087,10 +9085,10 @@
         <v>10</v>
       </c>
       <c r="D521" t="n">
-        <v>71.42935216127</v>
+        <v>198.158291790696</v>
       </c>
       <c r="E521" t="n">
-        <v>66.8033847819113</v>
+        <v>197.44686409916</v>
       </c>
     </row>
     <row r="522">
@@ -9104,10 +9102,10 @@
         <v>10</v>
       </c>
       <c r="D522" t="n">
-        <v>68.9183389088665</v>
+        <v>198.623663040932</v>
       </c>
       <c r="E522" t="n">
-        <v>67.3686602706803</v>
+        <v>197.589509630386</v>
       </c>
     </row>
     <row r="523">
@@ -9121,10 +9119,10 @@
         <v>10</v>
       </c>
       <c r="D523" t="n">
-        <v>72.2900150528474</v>
+        <v>198.9601608028</v>
       </c>
       <c r="E523" t="n">
-        <v>68.0732146530215</v>
+        <v>197.758015083167</v>
       </c>
     </row>
     <row r="524">
@@ -9138,10 +9136,10 @@
         <v>10</v>
       </c>
       <c r="D524" t="n">
-        <v>73.7961625773052</v>
+        <v>198.194328122039</v>
       </c>
       <c r="E524" t="n">
-        <v>68.8888826782582</v>
+        <v>197.859316521931</v>
       </c>
     </row>
     <row r="525">
@@ -9155,10 +9153,10 @@
         <v>10</v>
       </c>
       <c r="D525" t="n">
-        <v>73.6642081727159</v>
+        <v>198.280282462736</v>
       </c>
       <c r="E525" t="n">
-        <v>69.7113923851104</v>
+        <v>198.080348431506</v>
       </c>
     </row>
     <row r="526">
@@ -9172,10 +9170,10 @@
         <v>10</v>
       </c>
       <c r="D526" t="n">
-        <v>73.0846061909715</v>
+        <v>198.831414692704</v>
       </c>
       <c r="E526" t="n">
-        <v>70.3582611905438</v>
+        <v>198.207157453294</v>
       </c>
     </row>
     <row r="527">
@@ -9189,54 +9187,58 @@
         <v>10</v>
       </c>
       <c r="D527" t="n">
-        <v>73.5427033690746</v>
+        <v>199.468069183848</v>
       </c>
       <c r="E527" t="n">
-        <v>71.0341362315229</v>
+        <v>198.372763292745</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B528" s="1" t="n">
-        <v>43496</v>
+        <v>45747</v>
       </c>
       <c r="C528" t="n">
         <v>10</v>
       </c>
       <c r="D528" t="n">
-        <v>106.135476721793</v>
-      </c>
-      <c r="E528"/>
+        <v>200.105263099909</v>
+      </c>
+      <c r="E528" t="n">
+        <v>198.558829255895</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B529" s="1" t="n">
-        <v>43524</v>
+        <v>45777</v>
       </c>
       <c r="C529" t="n">
         <v>10</v>
       </c>
       <c r="D529" t="n">
-        <v>102.8274077081</v>
-      </c>
-      <c r="E529"/>
+        <v>199.900668796946</v>
+      </c>
+      <c r="E529" t="n">
+        <v>198.670357819922</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="s">
         <v>13</v>
       </c>
       <c r="B530" s="1" t="n">
-        <v>43555</v>
+        <v>43496</v>
       </c>
       <c r="C530" t="n">
         <v>10</v>
       </c>
       <c r="D530" t="n">
-        <v>99.2870665416581</v>
+        <v>64.0491020677844</v>
       </c>
       <c r="E530"/>
     </row>
@@ -9245,13 +9247,13 @@
         <v>13</v>
       </c>
       <c r="B531" s="1" t="n">
-        <v>43585</v>
+        <v>43524</v>
       </c>
       <c r="C531" t="n">
         <v>10</v>
       </c>
       <c r="D531" t="n">
-        <v>91.769578627109</v>
+        <v>61.82443611649</v>
       </c>
       <c r="E531"/>
     </row>
@@ -9260,13 +9262,13 @@
         <v>13</v>
       </c>
       <c r="B532" s="1" t="n">
-        <v>43616</v>
+        <v>43555</v>
       </c>
       <c r="C532" t="n">
         <v>10</v>
       </c>
       <c r="D532" t="n">
-        <v>88.9605316465442</v>
+        <v>60.6352266062756</v>
       </c>
       <c r="E532"/>
     </row>
@@ -9275,13 +9277,13 @@
         <v>13</v>
       </c>
       <c r="B533" s="1" t="n">
-        <v>43646</v>
+        <v>43585</v>
       </c>
       <c r="C533" t="n">
         <v>10</v>
       </c>
       <c r="D533" t="n">
-        <v>84.6162629046379</v>
+        <v>61.4159956467082</v>
       </c>
       <c r="E533"/>
     </row>
@@ -9290,13 +9292,13 @@
         <v>13</v>
       </c>
       <c r="B534" s="1" t="n">
-        <v>43677</v>
+        <v>43616</v>
       </c>
       <c r="C534" t="n">
         <v>10</v>
       </c>
       <c r="D534" t="n">
-        <v>83.5610291417867</v>
+        <v>58.9799837712983</v>
       </c>
       <c r="E534"/>
     </row>
@@ -9305,13 +9307,13 @@
         <v>13</v>
       </c>
       <c r="B535" s="1" t="n">
-        <v>43708</v>
+        <v>43646</v>
       </c>
       <c r="C535" t="n">
         <v>10</v>
       </c>
       <c r="D535" t="n">
-        <v>82.2083099996816</v>
+        <v>56.2904113042008</v>
       </c>
       <c r="E535"/>
     </row>
@@ -9320,13 +9322,13 @@
         <v>13</v>
       </c>
       <c r="B536" s="1" t="n">
-        <v>43738</v>
+        <v>43677</v>
       </c>
       <c r="C536" t="n">
         <v>10</v>
       </c>
       <c r="D536" t="n">
-        <v>79.6016917452232</v>
+        <v>53.8016850191522</v>
       </c>
       <c r="E536"/>
     </row>
@@ -9335,13 +9337,13 @@
         <v>13</v>
       </c>
       <c r="B537" s="1" t="n">
-        <v>43769</v>
+        <v>43708</v>
       </c>
       <c r="C537" t="n">
         <v>10</v>
       </c>
       <c r="D537" t="n">
-        <v>78.6393292673582</v>
+        <v>55.1402706172024</v>
       </c>
       <c r="E537"/>
     </row>
@@ -9350,13 +9352,13 @@
         <v>13</v>
       </c>
       <c r="B538" s="1" t="n">
-        <v>43799</v>
+        <v>43738</v>
       </c>
       <c r="C538" t="n">
         <v>10</v>
       </c>
       <c r="D538" t="n">
-        <v>77.2061883582041</v>
+        <v>54.0339910631902</v>
       </c>
       <c r="E538"/>
     </row>
@@ -9365,50 +9367,46 @@
         <v>13</v>
       </c>
       <c r="B539" s="1" t="n">
-        <v>43830</v>
+        <v>43769</v>
       </c>
       <c r="C539" t="n">
         <v>10</v>
       </c>
       <c r="D539" t="n">
-        <v>80.3143140060123</v>
-      </c>
-      <c r="E539" t="n">
-        <v>87.9272655556757</v>
-      </c>
+        <v>48.5741641237493</v>
+      </c>
+      <c r="E539"/>
     </row>
     <row r="540">
       <c r="A540" t="s">
         <v>13</v>
       </c>
       <c r="B540" s="1" t="n">
-        <v>43861</v>
+        <v>43799</v>
       </c>
       <c r="C540" t="n">
         <v>10</v>
       </c>
       <c r="D540" t="n">
-        <v>79.9767169413582</v>
-      </c>
-      <c r="E540" t="n">
-        <v>85.7473689073061</v>
-      </c>
+        <v>46.9947674627455</v>
+      </c>
+      <c r="E540"/>
     </row>
     <row r="541">
       <c r="A541" t="s">
         <v>13</v>
       </c>
       <c r="B541" s="1" t="n">
-        <v>43890</v>
+        <v>43830</v>
       </c>
       <c r="C541" t="n">
         <v>10</v>
       </c>
       <c r="D541" t="n">
-        <v>75.7712638369644</v>
+        <v>44.596413565117</v>
       </c>
       <c r="E541" t="n">
-        <v>83.4926902513782</v>
+        <v>55.5280372803262</v>
       </c>
     </row>
     <row r="542">
@@ -9416,16 +9414,16 @@
         <v>13</v>
       </c>
       <c r="B542" s="1" t="n">
-        <v>43921</v>
+        <v>43861</v>
       </c>
       <c r="C542" t="n">
         <v>10</v>
       </c>
       <c r="D542" t="n">
-        <v>72.0367132320456</v>
+        <v>45.8658461859098</v>
       </c>
       <c r="E542" t="n">
-        <v>81.2218274755771</v>
+        <v>54.0127659568366</v>
       </c>
     </row>
     <row r="543">
@@ -9433,16 +9431,16 @@
         <v>13</v>
       </c>
       <c r="B543" s="1" t="n">
-        <v>43951</v>
+        <v>43890</v>
       </c>
       <c r="C543" t="n">
         <v>10</v>
       </c>
       <c r="D543" t="n">
-        <v>71.9107326987685</v>
+        <v>45.1959267736983</v>
       </c>
       <c r="E543" t="n">
-        <v>79.5669236482154</v>
+        <v>52.6270568449373</v>
       </c>
     </row>
     <row r="544">
@@ -9450,16 +9448,16 @@
         <v>13</v>
       </c>
       <c r="B544" s="1" t="n">
-        <v>43982</v>
+        <v>43921</v>
       </c>
       <c r="C544" t="n">
         <v>10</v>
       </c>
       <c r="D544" t="n">
-        <v>70.725067950724</v>
+        <v>45.6485285739431</v>
       </c>
       <c r="E544" t="n">
-        <v>78.0473016735637</v>
+        <v>51.3781653422429</v>
       </c>
     </row>
     <row r="545">
@@ -9467,16 +9465,16 @@
         <v>13</v>
       </c>
       <c r="B545" s="1" t="n">
-        <v>44012</v>
+        <v>43951</v>
       </c>
       <c r="C545" t="n">
         <v>10</v>
       </c>
       <c r="D545" t="n">
-        <v>71.33517220661</v>
+        <v>45.0888245569265</v>
       </c>
       <c r="E545" t="n">
-        <v>76.9405441153947</v>
+        <v>50.0175677514278</v>
       </c>
     </row>
     <row r="546">
@@ -9484,16 +9482,16 @@
         <v>13</v>
       </c>
       <c r="B546" s="1" t="n">
-        <v>44043</v>
+        <v>43982</v>
       </c>
       <c r="C546" t="n">
         <v>10</v>
       </c>
       <c r="D546" t="n">
-        <v>75.4215117294889</v>
+        <v>44.9757110666744</v>
       </c>
       <c r="E546" t="n">
-        <v>76.2622509977032</v>
+        <v>48.8505450260425</v>
       </c>
     </row>
     <row r="547">
@@ -9501,16 +9499,16 @@
         <v>13</v>
       </c>
       <c r="B547" s="1" t="n">
-        <v>44074</v>
+        <v>44012</v>
       </c>
       <c r="C547" t="n">
         <v>10</v>
       </c>
       <c r="D547" t="n">
-        <v>75.4673814125726</v>
+        <v>42.9290498798745</v>
       </c>
       <c r="E547" t="n">
-        <v>75.7005069487775</v>
+        <v>47.7370982406819</v>
       </c>
     </row>
     <row r="548">
@@ -9518,16 +9516,16 @@
         <v>13</v>
       </c>
       <c r="B548" s="1" t="n">
-        <v>44104</v>
+        <v>44043</v>
       </c>
       <c r="C548" t="n">
         <v>10</v>
       </c>
       <c r="D548" t="n">
-        <v>74.7912001974262</v>
+        <v>42.0737622407422</v>
       </c>
       <c r="E548" t="n">
-        <v>75.2996326531277</v>
+        <v>46.7597713424811</v>
       </c>
     </row>
     <row r="549">
@@ -9535,16 +9533,16 @@
         <v>13</v>
       </c>
       <c r="B549" s="1" t="n">
-        <v>44135</v>
+        <v>44074</v>
       </c>
       <c r="C549" t="n">
         <v>10</v>
       </c>
       <c r="D549" t="n">
-        <v>77.2099733102858</v>
+        <v>43.8942130794083</v>
       </c>
       <c r="E549" t="n">
-        <v>75.180519656705</v>
+        <v>45.8225998809983</v>
       </c>
     </row>
     <row r="550">
@@ -9552,16 +9550,16 @@
         <v>13</v>
       </c>
       <c r="B550" s="1" t="n">
-        <v>44165</v>
+        <v>44104</v>
       </c>
       <c r="C550" t="n">
         <v>10</v>
       </c>
       <c r="D550" t="n">
-        <v>71.9965739234484</v>
+        <v>43.4821484486287</v>
       </c>
       <c r="E550" t="n">
-        <v>74.7463851204754</v>
+        <v>44.9432796631181</v>
       </c>
     </row>
     <row r="551">
@@ -9569,16 +9567,16 @@
         <v>13</v>
       </c>
       <c r="B551" s="1" t="n">
-        <v>44196</v>
+        <v>44135</v>
       </c>
       <c r="C551" t="n">
         <v>10</v>
       </c>
       <c r="D551" t="n">
-        <v>72.0485657680656</v>
+        <v>43.840548493883</v>
       </c>
       <c r="E551" t="n">
-        <v>74.0575727673132</v>
+        <v>44.5488116939626</v>
       </c>
     </row>
     <row r="552">
@@ -9586,16 +9584,16 @@
         <v>13</v>
       </c>
       <c r="B552" s="1" t="n">
-        <v>44227</v>
+        <v>44165</v>
       </c>
       <c r="C552" t="n">
         <v>10</v>
       </c>
       <c r="D552" t="n">
-        <v>72.2695396765196</v>
+        <v>43.890692946002</v>
       </c>
       <c r="E552" t="n">
-        <v>73.4153079952433</v>
+        <v>44.2901388175673</v>
       </c>
     </row>
     <row r="553">
@@ -9603,16 +9601,16 @@
         <v>13</v>
       </c>
       <c r="B553" s="1" t="n">
-        <v>44255</v>
+        <v>44196</v>
       </c>
       <c r="C553" t="n">
         <v>10</v>
       </c>
       <c r="D553" t="n">
-        <v>72.3602932496758</v>
+        <v>45.9908264862381</v>
       </c>
       <c r="E553" t="n">
-        <v>73.1310604463026</v>
+        <v>44.4063398943274</v>
       </c>
     </row>
     <row r="554">
@@ -9620,16 +9618,16 @@
         <v>13</v>
       </c>
       <c r="B554" s="1" t="n">
-        <v>44286</v>
+        <v>44227</v>
       </c>
       <c r="C554" t="n">
         <v>10</v>
       </c>
       <c r="D554" t="n">
-        <v>72.1790812549829</v>
+        <v>43.0178676559709</v>
       </c>
       <c r="E554" t="n">
-        <v>73.142924448214</v>
+        <v>44.1690083501658</v>
       </c>
     </row>
     <row r="555">
@@ -9637,16 +9635,16 @@
         <v>13</v>
       </c>
       <c r="B555" s="1" t="n">
-        <v>44316</v>
+        <v>44255</v>
       </c>
       <c r="C555" t="n">
         <v>10</v>
       </c>
       <c r="D555" t="n">
-        <v>72.3829069091832</v>
+        <v>45.8257259880181</v>
       </c>
       <c r="E555" t="n">
-        <v>73.1822722990819</v>
+        <v>44.2214916180258</v>
       </c>
     </row>
     <row r="556">
@@ -9654,16 +9652,16 @@
         <v>13</v>
       </c>
       <c r="B556" s="1" t="n">
-        <v>44347</v>
+        <v>44286</v>
       </c>
       <c r="C556" t="n">
         <v>10</v>
       </c>
       <c r="D556" t="n">
-        <v>78.3965869882104</v>
+        <v>45.7049284455735</v>
       </c>
       <c r="E556" t="n">
-        <v>73.8215655522058</v>
+        <v>44.2261916073283</v>
       </c>
     </row>
     <row r="557">
@@ -9671,16 +9669,16 @@
         <v>13</v>
       </c>
       <c r="B557" s="1" t="n">
-        <v>44377</v>
+        <v>44316</v>
       </c>
       <c r="C557" t="n">
         <v>10</v>
       </c>
       <c r="D557" t="n">
-        <v>79.3338637228056</v>
+        <v>45.4813284829068</v>
       </c>
       <c r="E557" t="n">
-        <v>74.4881231785554</v>
+        <v>44.2589002678267</v>
       </c>
     </row>
     <row r="558">
@@ -9688,16 +9686,16 @@
         <v>13</v>
       </c>
       <c r="B558" s="1" t="n">
-        <v>44408</v>
+        <v>44347</v>
       </c>
       <c r="C558" t="n">
         <v>10</v>
       </c>
       <c r="D558" t="n">
-        <v>84.5133094829862</v>
+        <v>46.584096899323</v>
       </c>
       <c r="E558" t="n">
-        <v>75.2457729913469</v>
+        <v>44.3929324205474</v>
       </c>
     </row>
     <row r="559">
@@ -9705,16 +9703,16 @@
         <v>13</v>
       </c>
       <c r="B559" s="1" t="n">
-        <v>44439</v>
+        <v>44377</v>
       </c>
       <c r="C559" t="n">
         <v>10</v>
       </c>
       <c r="D559" t="n">
-        <v>88.7146181675197</v>
+        <v>47.0840412931037</v>
       </c>
       <c r="E559" t="n">
-        <v>76.3497093875924</v>
+        <v>44.7391817049832</v>
       </c>
     </row>
     <row r="560">
@@ -9722,16 +9720,16 @@
         <v>13</v>
       </c>
       <c r="B560" s="1" t="n">
-        <v>44469</v>
+        <v>44408</v>
       </c>
       <c r="C560" t="n">
         <v>10</v>
       </c>
       <c r="D560" t="n">
-        <v>85.7281916964925</v>
+        <v>47.1245762632958</v>
       </c>
       <c r="E560" t="n">
-        <v>77.261125345848</v>
+        <v>45.1600828735293</v>
       </c>
     </row>
     <row r="561">
@@ -9739,16 +9737,16 @@
         <v>13</v>
       </c>
       <c r="B561" s="1" t="n">
-        <v>44500</v>
+        <v>44439</v>
       </c>
       <c r="C561" t="n">
         <v>10</v>
       </c>
       <c r="D561" t="n">
-        <v>88.4269572167802</v>
+        <v>47.4451526704188</v>
       </c>
       <c r="E561" t="n">
-        <v>78.1958740047225</v>
+        <v>45.4559945061135</v>
       </c>
     </row>
     <row r="562">
@@ -9756,16 +9754,16 @@
         <v>13</v>
       </c>
       <c r="B562" s="1" t="n">
-        <v>44530</v>
+        <v>44469</v>
       </c>
       <c r="C562" t="n">
         <v>10</v>
       </c>
       <c r="D562" t="n">
-        <v>87.1332821224828</v>
+        <v>47.1436184701266</v>
       </c>
       <c r="E562" t="n">
-        <v>79.457266354642</v>
+        <v>45.761117007905</v>
       </c>
     </row>
     <row r="563">
@@ -9773,16 +9771,16 @@
         <v>13</v>
       </c>
       <c r="B563" s="1" t="n">
-        <v>44561</v>
+        <v>44500</v>
       </c>
       <c r="C563" t="n">
         <v>10</v>
       </c>
       <c r="D563" t="n">
-        <v>83.1089646400721</v>
+        <v>48.2469082598945</v>
       </c>
       <c r="E563" t="n">
-        <v>80.3789662606426</v>
+        <v>46.1283136550727</v>
       </c>
     </row>
     <row r="564">
@@ -9790,16 +9788,16 @@
         <v>13</v>
       </c>
       <c r="B564" s="1" t="n">
-        <v>44592</v>
+        <v>44530</v>
       </c>
       <c r="C564" t="n">
         <v>10</v>
       </c>
       <c r="D564" t="n">
-        <v>83.3510115253494</v>
+        <v>49.6306163820841</v>
       </c>
       <c r="E564" t="n">
-        <v>81.3024222480451</v>
+        <v>46.6066406080795</v>
       </c>
     </row>
     <row r="565">
@@ -9807,16 +9805,16 @@
         <v>13</v>
       </c>
       <c r="B565" s="1" t="n">
-        <v>44620</v>
+        <v>44561</v>
       </c>
       <c r="C565" t="n">
         <v>10</v>
       </c>
       <c r="D565" t="n">
-        <v>83.5390377252012</v>
+        <v>52.3959774066045</v>
       </c>
       <c r="E565" t="n">
-        <v>82.2339842876722</v>
+        <v>47.1404031847767</v>
       </c>
     </row>
     <row r="566">
@@ -9824,16 +9822,16 @@
         <v>13</v>
       </c>
       <c r="B566" s="1" t="n">
-        <v>44651</v>
+        <v>44592</v>
       </c>
       <c r="C566" t="n">
         <v>10</v>
       </c>
       <c r="D566" t="n">
-        <v>82.2559884588231</v>
+        <v>50.1677625656606</v>
       </c>
       <c r="E566" t="n">
-        <v>83.0737265546589</v>
+        <v>47.7362277605842</v>
       </c>
     </row>
     <row r="567">
@@ -9841,16 +9839,16 @@
         <v>13</v>
       </c>
       <c r="B567" s="1" t="n">
-        <v>44681</v>
+        <v>44620</v>
       </c>
       <c r="C567" t="n">
         <v>10</v>
       </c>
       <c r="D567" t="n">
-        <v>82.2147518278186</v>
+        <v>54.0515156251754</v>
       </c>
       <c r="E567" t="n">
-        <v>83.8930469645451</v>
+        <v>48.4217102303473</v>
       </c>
     </row>
     <row r="568">
@@ -9858,16 +9856,16 @@
         <v>13</v>
       </c>
       <c r="B568" s="1" t="n">
-        <v>44712</v>
+        <v>44651</v>
       </c>
       <c r="C568" t="n">
         <v>10</v>
       </c>
       <c r="D568" t="n">
-        <v>82.6688109920672</v>
+        <v>55.6102871040039</v>
       </c>
       <c r="E568" t="n">
-        <v>84.2490656315332</v>
+        <v>49.2471567852165</v>
       </c>
     </row>
     <row r="569">
@@ -9875,16 +9873,16 @@
         <v>13</v>
       </c>
       <c r="B569" s="1" t="n">
-        <v>44742</v>
+        <v>44681</v>
       </c>
       <c r="C569" t="n">
         <v>10</v>
       </c>
       <c r="D569" t="n">
-        <v>87.9437961994899</v>
+        <v>56.080347683551</v>
       </c>
       <c r="E569" t="n">
-        <v>84.9665600045902</v>
+        <v>50.1304083852702</v>
       </c>
     </row>
     <row r="570">
@@ -9892,16 +9890,16 @@
         <v>13</v>
       </c>
       <c r="B570" s="1" t="n">
-        <v>44773</v>
+        <v>44712</v>
       </c>
       <c r="C570" t="n">
         <v>10</v>
       </c>
       <c r="D570" t="n">
-        <v>88.0851136989694</v>
+        <v>56.7503238301069</v>
       </c>
       <c r="E570" t="n">
-        <v>85.2642103559222</v>
+        <v>50.9775939628355</v>
       </c>
     </row>
     <row r="571">
@@ -9909,16 +9907,16 @@
         <v>13</v>
       </c>
       <c r="B571" s="1" t="n">
-        <v>44804</v>
+        <v>44742</v>
       </c>
       <c r="C571" t="n">
         <v>10</v>
       </c>
       <c r="D571" t="n">
-        <v>90.9163173795506</v>
+        <v>55.3149417994787</v>
       </c>
       <c r="E571" t="n">
-        <v>85.4476852902581</v>
+        <v>51.6635023383667</v>
       </c>
     </row>
     <row r="572">
@@ -9926,16 +9924,16 @@
         <v>13</v>
       </c>
       <c r="B572" s="1" t="n">
-        <v>44834</v>
+        <v>44773</v>
       </c>
       <c r="C572" t="n">
         <v>10</v>
       </c>
       <c r="D572" t="n">
-        <v>88.8353404449253</v>
+        <v>57.3015962094963</v>
       </c>
       <c r="E572" t="n">
-        <v>85.7066143526275</v>
+        <v>52.5115873338834</v>
       </c>
     </row>
     <row r="573">
@@ -9943,16 +9941,16 @@
         <v>13</v>
       </c>
       <c r="B573" s="1" t="n">
-        <v>44865</v>
+        <v>44804</v>
       </c>
       <c r="C573" t="n">
         <v>10</v>
       </c>
       <c r="D573" t="n">
-        <v>88.3948578560411</v>
+        <v>55.839796755695</v>
       </c>
       <c r="E573" t="n">
-        <v>85.7039394058992</v>
+        <v>53.2111410076565</v>
       </c>
     </row>
     <row r="574">
@@ -9960,16 +9958,16 @@
         <v>13</v>
       </c>
       <c r="B574" s="1" t="n">
-        <v>44895</v>
+        <v>44834</v>
       </c>
       <c r="C574" t="n">
         <v>10</v>
       </c>
       <c r="D574" t="n">
-        <v>86.6295898779392</v>
+        <v>58.4100577529056</v>
       </c>
       <c r="E574" t="n">
-        <v>85.6619650521873</v>
+        <v>54.150010947888</v>
       </c>
     </row>
     <row r="575">
@@ -9977,16 +9975,16 @@
         <v>13</v>
       </c>
       <c r="B575" s="1" t="n">
-        <v>44926</v>
+        <v>44865</v>
       </c>
       <c r="C575" t="n">
         <v>10</v>
       </c>
       <c r="D575" t="n">
-        <v>82.5445852884514</v>
+        <v>61.459102509436</v>
       </c>
       <c r="E575" t="n">
-        <v>85.6149334395522</v>
+        <v>55.2510271353498</v>
       </c>
     </row>
     <row r="576">
@@ -9994,16 +9992,16 @@
         <v>13</v>
       </c>
       <c r="B576" s="1" t="n">
-        <v>44957</v>
+        <v>44895</v>
       </c>
       <c r="C576" t="n">
         <v>10</v>
       </c>
       <c r="D576" t="n">
-        <v>81.8254928445596</v>
+        <v>63.1555939290306</v>
       </c>
       <c r="E576" t="n">
-        <v>85.4878068828197</v>
+        <v>56.3781085975954</v>
       </c>
     </row>
     <row r="577">
@@ -10011,16 +10009,16 @@
         <v>13</v>
       </c>
       <c r="B577" s="1" t="n">
-        <v>44985</v>
+        <v>44926</v>
       </c>
       <c r="C577" t="n">
         <v>10</v>
       </c>
       <c r="D577" t="n">
-        <v>81.7718638572031</v>
+        <v>59.9914693942271</v>
       </c>
       <c r="E577" t="n">
-        <v>85.3405423938199</v>
+        <v>57.0110662632306</v>
       </c>
     </row>
     <row r="578">
@@ -10028,16 +10026,16 @@
         <v>13</v>
       </c>
       <c r="B578" s="1" t="n">
-        <v>45016</v>
+        <v>44957</v>
       </c>
       <c r="C578" t="n">
         <v>10</v>
       </c>
       <c r="D578" t="n">
-        <v>84.8647527996633</v>
+        <v>57.8498393344469</v>
       </c>
       <c r="E578" t="n">
-        <v>85.5579394222232</v>
+        <v>57.6512393272961</v>
       </c>
     </row>
     <row r="579">
@@ -10045,16 +10043,16 @@
         <v>13</v>
       </c>
       <c r="B579" s="1" t="n">
-        <v>45046</v>
+        <v>44985</v>
       </c>
       <c r="C579" t="n">
         <v>10</v>
       </c>
       <c r="D579" t="n">
-        <v>83.8007302002446</v>
+        <v>56.8784070481634</v>
       </c>
       <c r="E579" t="n">
-        <v>85.6901042865921</v>
+        <v>57.8868136125451</v>
       </c>
     </row>
     <row r="580">
@@ -10062,16 +10060,16 @@
         <v>13</v>
       </c>
       <c r="B580" s="1" t="n">
-        <v>45077</v>
+        <v>45016</v>
       </c>
       <c r="C580" t="n">
         <v>10</v>
       </c>
       <c r="D580" t="n">
-        <v>86.6652928096498</v>
+        <v>56.364232487318</v>
       </c>
       <c r="E580" t="n">
-        <v>86.0231444380573</v>
+        <v>57.949642394488</v>
       </c>
     </row>
     <row r="581">
@@ -10079,16 +10077,16 @@
         <v>13</v>
       </c>
       <c r="B581" s="1" t="n">
-        <v>45107</v>
+        <v>45046</v>
       </c>
       <c r="C581" t="n">
         <v>10</v>
       </c>
       <c r="D581" t="n">
-        <v>85.9672754669865</v>
+        <v>60.5983814579239</v>
       </c>
       <c r="E581" t="n">
-        <v>85.8584343770153</v>
+        <v>58.326145209019</v>
       </c>
     </row>
     <row r="582">
@@ -10096,16 +10094,16 @@
         <v>13</v>
       </c>
       <c r="B582" s="1" t="n">
-        <v>45138</v>
+        <v>45077</v>
       </c>
       <c r="C582" t="n">
         <v>10</v>
       </c>
       <c r="D582" t="n">
-        <v>86.7309211162566</v>
+        <v>62.9413452381541</v>
       </c>
       <c r="E582" t="n">
-        <v>85.7455849951226</v>
+        <v>58.8420636596896</v>
       </c>
     </row>
     <row r="583">
@@ -10113,16 +10111,16 @@
         <v>13</v>
       </c>
       <c r="B583" s="1" t="n">
-        <v>45169</v>
+        <v>45107</v>
       </c>
       <c r="C583" t="n">
         <v>10</v>
       </c>
       <c r="D583" t="n">
-        <v>87.6872921605799</v>
+        <v>61.0691303286673</v>
       </c>
       <c r="E583" t="n">
-        <v>85.4764995602084</v>
+        <v>59.3215793704554</v>
       </c>
     </row>
     <row r="584">
@@ -10130,16 +10128,16 @@
         <v>13</v>
       </c>
       <c r="B584" s="1" t="n">
-        <v>45199</v>
+        <v>45138</v>
       </c>
       <c r="C584" t="n">
         <v>10</v>
       </c>
       <c r="D584" t="n">
-        <v>89.0247176902273</v>
+        <v>61.1007013020983</v>
       </c>
       <c r="E584" t="n">
-        <v>85.4922809973169</v>
+        <v>59.6381714615055</v>
       </c>
     </row>
     <row r="585">
@@ -10147,16 +10145,16 @@
         <v>13</v>
       </c>
       <c r="B585" s="1" t="n">
-        <v>45230</v>
+        <v>45169</v>
       </c>
       <c r="C585" t="n">
         <v>10</v>
       </c>
       <c r="D585" t="n">
-        <v>88.4716230721895</v>
+        <v>64.1746175176083</v>
       </c>
       <c r="E585" t="n">
-        <v>85.4986780986626</v>
+        <v>60.3327398583316</v>
       </c>
     </row>
     <row r="586">
@@ -10164,16 +10162,16 @@
         <v>13</v>
       </c>
       <c r="B586" s="1" t="n">
-        <v>45260</v>
+        <v>45199</v>
       </c>
       <c r="C586" t="n">
         <v>10</v>
       </c>
       <c r="D586" t="n">
-        <v>88.3883002240841</v>
+        <v>62.1350330436377</v>
       </c>
       <c r="E586" t="n">
-        <v>85.6452372941746</v>
+        <v>60.6431544658926</v>
       </c>
     </row>
     <row r="587">
@@ -10181,16 +10179,16 @@
         <v>13</v>
       </c>
       <c r="B587" s="1" t="n">
-        <v>45291</v>
+        <v>45230</v>
       </c>
       <c r="C587" t="n">
         <v>10</v>
       </c>
       <c r="D587" t="n">
-        <v>91.9608852928247</v>
+        <v>63.8353624647531</v>
       </c>
       <c r="E587" t="n">
-        <v>86.4299289612057</v>
+        <v>60.8411761288357</v>
       </c>
     </row>
     <row r="588">
@@ -10198,16 +10196,16 @@
         <v>13</v>
       </c>
       <c r="B588" s="1" t="n">
-        <v>45322</v>
+        <v>45260</v>
       </c>
       <c r="C588" t="n">
         <v>10</v>
       </c>
       <c r="D588" t="n">
-        <v>91.233334199971</v>
+        <v>64.0081462744648</v>
       </c>
       <c r="E588" t="n">
-        <v>87.2139157408234</v>
+        <v>60.9122221576219</v>
       </c>
     </row>
     <row r="589">
@@ -10215,16 +10213,16 @@
         <v>13</v>
       </c>
       <c r="B589" s="1" t="n">
-        <v>45351</v>
+        <v>45291</v>
       </c>
       <c r="C589" t="n">
         <v>10</v>
       </c>
       <c r="D589" t="n">
-        <v>94.9818608631427</v>
+        <v>63.7940916904896</v>
       </c>
       <c r="E589" t="n">
-        <v>88.3147488246517</v>
+        <v>61.2291073489771</v>
       </c>
     </row>
     <row r="590">
@@ -10232,16 +10230,16 @@
         <v>13</v>
       </c>
       <c r="B590" s="1" t="n">
-        <v>45382</v>
+        <v>45322</v>
       </c>
       <c r="C590" t="n">
         <v>10</v>
       </c>
       <c r="D590" t="n">
-        <v>93.2189455025761</v>
+        <v>65.3221805257711</v>
       </c>
       <c r="E590" t="n">
-        <v>89.0109315498944</v>
+        <v>61.8518024482541</v>
       </c>
     </row>
     <row r="591">
@@ -10249,16 +10247,16 @@
         <v>13</v>
       </c>
       <c r="B591" s="1" t="n">
-        <v>45412</v>
+        <v>45351</v>
       </c>
       <c r="C591" t="n">
         <v>10</v>
       </c>
       <c r="D591" t="n">
-        <v>94.4923773273482</v>
+        <v>65.4322028773246</v>
       </c>
       <c r="E591" t="n">
-        <v>89.9019021438197</v>
+        <v>62.5646187673509</v>
       </c>
     </row>
     <row r="592">
@@ -10266,16 +10264,16 @@
         <v>13</v>
       </c>
       <c r="B592" s="1" t="n">
-        <v>45443</v>
+        <v>45382</v>
       </c>
       <c r="C592" t="n">
         <v>10</v>
       </c>
       <c r="D592" t="n">
-        <v>94.7468304885008</v>
+        <v>68.1999215365208</v>
       </c>
       <c r="E592" t="n">
-        <v>90.5753636170573</v>
+        <v>63.5509261881178</v>
       </c>
     </row>
     <row r="593">
@@ -10283,16 +10281,16 @@
         <v>13</v>
       </c>
       <c r="B593" s="1" t="n">
-        <v>45473</v>
+        <v>45412</v>
       </c>
       <c r="C593" t="n">
         <v>10</v>
       </c>
       <c r="D593" t="n">
-        <v>94.6504424021756</v>
+        <v>68.1950801855598</v>
       </c>
       <c r="E593" t="n">
-        <v>91.2989608616564</v>
+        <v>64.1839844154208</v>
       </c>
     </row>
     <row r="594">
@@ -10300,16 +10298,16 @@
         <v>13</v>
       </c>
       <c r="B594" s="1" t="n">
-        <v>45504</v>
+        <v>45443</v>
       </c>
       <c r="C594" t="n">
         <v>10</v>
       </c>
       <c r="D594" t="n">
-        <v>97.542484196831</v>
+        <v>68.5149821612973</v>
       </c>
       <c r="E594" t="n">
-        <v>92.1999244517042</v>
+        <v>64.6484541590161</v>
       </c>
     </row>
     <row r="595">
@@ -10317,16 +10315,16 @@
         <v>13</v>
       </c>
       <c r="B595" s="1" t="n">
-        <v>45535</v>
+        <v>45473</v>
       </c>
       <c r="C595" t="n">
         <v>10</v>
       </c>
       <c r="D595" t="n">
-        <v>100.047904360493</v>
+        <v>68.437945654661</v>
       </c>
       <c r="E595" t="n">
-        <v>93.2299754683637</v>
+        <v>65.2625221028489</v>
       </c>
     </row>
     <row r="596">
@@ -10334,16 +10332,16 @@
         <v>13</v>
       </c>
       <c r="B596" s="1" t="n">
-        <v>45565</v>
+        <v>45504</v>
       </c>
       <c r="C596" t="n">
         <v>10</v>
       </c>
       <c r="D596" t="n">
-        <v>105.289073057232</v>
+        <v>72.3363188071854</v>
       </c>
       <c r="E596" t="n">
-        <v>94.5853384156141</v>
+        <v>66.1988235616061</v>
       </c>
     </row>
     <row r="597">
@@ -10351,16 +10349,16 @@
         <v>13</v>
       </c>
       <c r="B597" s="1" t="n">
-        <v>45596</v>
+        <v>45535</v>
       </c>
       <c r="C597" t="n">
         <v>10</v>
       </c>
       <c r="D597" t="n">
-        <v>104.539049909486</v>
+        <v>71.42935216127</v>
       </c>
       <c r="E597" t="n">
-        <v>95.9242906520555</v>
+        <v>66.8033847819113</v>
       </c>
     </row>
     <row r="598">
@@ -10368,16 +10366,16 @@
         <v>13</v>
       </c>
       <c r="B598" s="1" t="n">
-        <v>45626</v>
+        <v>45565</v>
       </c>
       <c r="C598" t="n">
         <v>10</v>
       </c>
       <c r="D598" t="n">
-        <v>104.638195728519</v>
+        <v>68.9183389088665</v>
       </c>
       <c r="E598" t="n">
-        <v>97.2784486107584</v>
+        <v>67.3686602706803</v>
       </c>
     </row>
     <row r="599">
@@ -10385,16 +10383,16 @@
         <v>13</v>
       </c>
       <c r="B599" s="1" t="n">
-        <v>45657</v>
+        <v>45596</v>
       </c>
       <c r="C599" t="n">
         <v>10</v>
       </c>
       <c r="D599" t="n">
-        <v>106.616180652463</v>
+        <v>72.2900150528474</v>
       </c>
       <c r="E599" t="n">
-        <v>98.4997232240616</v>
+        <v>68.0732146530215</v>
       </c>
     </row>
     <row r="600">
@@ -10402,16 +10400,16 @@
         <v>13</v>
       </c>
       <c r="B600" s="1" t="n">
-        <v>45688</v>
+        <v>45626</v>
       </c>
       <c r="C600" t="n">
         <v>10</v>
       </c>
       <c r="D600" t="n">
-        <v>106.603541318742</v>
+        <v>73.7961625773052</v>
       </c>
       <c r="E600" t="n">
-        <v>99.7805738172925</v>
+        <v>68.8888826782582</v>
       </c>
     </row>
     <row r="601">
@@ -10419,16 +10417,16 @@
         <v>13</v>
       </c>
       <c r="B601" s="1" t="n">
-        <v>45716</v>
+        <v>45657</v>
       </c>
       <c r="C601" t="n">
         <v>10</v>
       </c>
       <c r="D601" t="n">
-        <v>106.559298914382</v>
+        <v>73.6642081727159</v>
       </c>
       <c r="E601" t="n">
-        <v>100.745360321562</v>
+        <v>69.7113923851104</v>
       </c>
     </row>
     <row r="602">
@@ -10436,16 +10434,16 @@
         <v>13</v>
       </c>
       <c r="B602" s="1" t="n">
-        <v>45747</v>
+        <v>45688</v>
       </c>
       <c r="C602" t="n">
         <v>10</v>
       </c>
       <c r="D602" t="n">
-        <v>106.536546966904</v>
+        <v>73.0846061909715</v>
       </c>
       <c r="E602" t="n">
-        <v>101.85516044359</v>
+        <v>70.3582611905438</v>
       </c>
     </row>
     <row r="603">
@@ -10453,16 +10451,16 @@
         <v>13</v>
       </c>
       <c r="B603" s="1" t="n">
-        <v>45777</v>
+        <v>45716</v>
       </c>
       <c r="C603" t="n">
         <v>10</v>
       </c>
       <c r="D603" t="n">
-        <v>109.385893336664</v>
+        <v>73.5427033690746</v>
       </c>
       <c r="E603" t="n">
-        <v>103.096286777699</v>
+        <v>71.034136231523</v>
       </c>
     </row>
     <row r="604">
@@ -10476,7 +10474,7 @@
         <v>10</v>
       </c>
       <c r="D604" t="n">
-        <v>412.817884216087</v>
+        <v>106.135476721793</v>
       </c>
       <c r="E604"/>
     </row>
@@ -10491,7 +10489,7 @@
         <v>10</v>
       </c>
       <c r="D605" t="n">
-        <v>396.209781519341</v>
+        <v>102.8274077081</v>
       </c>
       <c r="E605"/>
     </row>
@@ -10506,7 +10504,7 @@
         <v>10</v>
       </c>
       <c r="D606" t="n">
-        <v>390.522691912943</v>
+        <v>99.2870665416581</v>
       </c>
       <c r="E606"/>
     </row>
@@ -10521,7 +10519,7 @@
         <v>10</v>
       </c>
       <c r="D607" t="n">
-        <v>397.893359864306</v>
+        <v>91.769578627109</v>
       </c>
       <c r="E607"/>
     </row>
@@ -10536,7 +10534,7 @@
         <v>10</v>
       </c>
       <c r="D608" t="n">
-        <v>407.153238657217</v>
+        <v>88.9605316465442</v>
       </c>
       <c r="E608"/>
     </row>
@@ -10551,7 +10549,7 @@
         <v>10</v>
       </c>
       <c r="D609" t="n">
-        <v>401.157472570662</v>
+        <v>84.6162629046379</v>
       </c>
       <c r="E609"/>
     </row>
@@ -10566,7 +10564,7 @@
         <v>10</v>
       </c>
       <c r="D610" t="n">
-        <v>380.078264807365</v>
+        <v>83.5610291417867</v>
       </c>
       <c r="E610"/>
     </row>
@@ -10581,7 +10579,7 @@
         <v>10</v>
       </c>
       <c r="D611" t="n">
-        <v>381.754817118344</v>
+        <v>82.2083099996816</v>
       </c>
       <c r="E611"/>
     </row>
@@ -10596,7 +10594,7 @@
         <v>10</v>
       </c>
       <c r="D612" t="n">
-        <v>387.45680748447</v>
+        <v>79.6016917452232</v>
       </c>
       <c r="E612"/>
     </row>
@@ -10611,7 +10609,7 @@
         <v>10</v>
       </c>
       <c r="D613" t="n">
-        <v>396.039517789037</v>
+        <v>78.6393292673582</v>
       </c>
       <c r="E613"/>
     </row>
@@ -10626,7 +10624,7 @@
         <v>10</v>
       </c>
       <c r="D614" t="n">
-        <v>403.389872196782</v>
+        <v>77.2061883582041</v>
       </c>
       <c r="E614"/>
     </row>
@@ -10641,10 +10639,10 @@
         <v>10</v>
       </c>
       <c r="D615" t="n">
-        <v>407.25857631424</v>
+        <v>80.3143140060123</v>
       </c>
       <c r="E615" t="n">
-        <v>396.811023704233</v>
+        <v>87.9272655556757</v>
       </c>
     </row>
     <row r="616">
@@ -10658,10 +10656,10 @@
         <v>10</v>
       </c>
       <c r="D616" t="n">
-        <v>411.332588889511</v>
+        <v>79.9767169413582</v>
       </c>
       <c r="E616" t="n">
-        <v>396.687249093685</v>
+        <v>85.7473689073061</v>
       </c>
     </row>
     <row r="617">
@@ -10675,10 +10673,10 @@
         <v>10</v>
       </c>
       <c r="D617" t="n">
-        <v>416.625160709244</v>
+        <v>75.7712638369644</v>
       </c>
       <c r="E617" t="n">
-        <v>398.388530692844</v>
+        <v>83.4926902513782</v>
       </c>
     </row>
     <row r="618">
@@ -10692,10 +10690,10 @@
         <v>10</v>
       </c>
       <c r="D618" t="n">
-        <v>424.774808548245</v>
+        <v>72.0367132320456</v>
       </c>
       <c r="E618" t="n">
-        <v>401.242873745785</v>
+        <v>81.2218274755771</v>
       </c>
     </row>
     <row r="619">
@@ -10709,10 +10707,10 @@
         <v>10</v>
       </c>
       <c r="D619" t="n">
-        <v>446.704185306581</v>
+        <v>71.9107326987685</v>
       </c>
       <c r="E619" t="n">
-        <v>405.310442532642</v>
+        <v>79.5669236482154</v>
       </c>
     </row>
     <row r="620">
@@ -10726,10 +10724,10 @@
         <v>10</v>
       </c>
       <c r="D620" t="n">
-        <v>441.728312947805</v>
+        <v>70.725067950724</v>
       </c>
       <c r="E620" t="n">
-        <v>408.191698723524</v>
+        <v>78.0473016735637</v>
       </c>
     </row>
     <row r="621">
@@ -10743,10 +10741,10 @@
         <v>10</v>
       </c>
       <c r="D621" t="n">
-        <v>445.232083763989</v>
+        <v>71.33517220661</v>
       </c>
       <c r="E621" t="n">
-        <v>411.864582989634</v>
+        <v>76.9405441153947</v>
       </c>
     </row>
     <row r="622">
@@ -10760,10 +10758,10 @@
         <v>10</v>
       </c>
       <c r="D622" t="n">
-        <v>431.173839294761</v>
+        <v>75.4215117294889</v>
       </c>
       <c r="E622" t="n">
-        <v>416.122547530251</v>
+        <v>76.2622509977032</v>
       </c>
     </row>
     <row r="623">
@@ -10777,10 +10775,10 @@
         <v>10</v>
       </c>
       <c r="D623" t="n">
-        <v>439.621632714023</v>
+        <v>75.4673814125726</v>
       </c>
       <c r="E623" t="n">
-        <v>420.944782163224</v>
+        <v>75.7005069487775</v>
       </c>
     </row>
     <row r="624">
@@ -10794,10 +10792,10 @@
         <v>10</v>
       </c>
       <c r="D624" t="n">
-        <v>465.753697542433</v>
+        <v>74.7912001974262</v>
       </c>
       <c r="E624" t="n">
-        <v>427.469523001388</v>
+        <v>75.2996326531277</v>
       </c>
     </row>
     <row r="625">
@@ -10811,10 +10809,10 @@
         <v>10</v>
       </c>
       <c r="D625" t="n">
-        <v>464.03577482462</v>
+        <v>77.2099733102858</v>
       </c>
       <c r="E625" t="n">
-        <v>433.135877754353</v>
+        <v>75.180519656705</v>
       </c>
     </row>
     <row r="626">
@@ -10828,10 +10826,10 @@
         <v>10</v>
       </c>
       <c r="D626" t="n">
-        <v>469.046247471819</v>
+        <v>71.9965739234484</v>
       </c>
       <c r="E626" t="n">
-        <v>438.607242360606</v>
+        <v>74.7463851204754</v>
       </c>
     </row>
     <row r="627">
@@ -10845,10 +10843,10 @@
         <v>10</v>
       </c>
       <c r="D627" t="n">
-        <v>476.971523413689</v>
+        <v>72.0485657680656</v>
       </c>
       <c r="E627" t="n">
-        <v>444.416654618893</v>
+        <v>74.0575727673132</v>
       </c>
     </row>
     <row r="628">
@@ -10862,10 +10860,10 @@
         <v>10</v>
       </c>
       <c r="D628" t="n">
-        <v>491.463027568651</v>
+        <v>72.2695396765196</v>
       </c>
       <c r="E628" t="n">
-        <v>451.094191175488</v>
+        <v>73.4153079952433</v>
       </c>
     </row>
     <row r="629">
@@ -10879,10 +10877,10 @@
         <v>10</v>
       </c>
       <c r="D629" t="n">
-        <v>485.854331500654</v>
+        <v>72.3602932496758</v>
       </c>
       <c r="E629" t="n">
-        <v>456.863288741439</v>
+        <v>73.1310604463026</v>
       </c>
     </row>
     <row r="630">
@@ -10896,10 +10894,10 @@
         <v>10</v>
       </c>
       <c r="D630" t="n">
-        <v>494.88296510663</v>
+        <v>72.1790812549829</v>
       </c>
       <c r="E630" t="n">
-        <v>462.705635121305</v>
+        <v>73.142924448214</v>
       </c>
     </row>
     <row r="631">
@@ -10913,10 +10911,10 @@
         <v>10</v>
       </c>
       <c r="D631" t="n">
-        <v>493.881982300246</v>
+        <v>72.3829069091832</v>
       </c>
       <c r="E631" t="n">
-        <v>466.63711820411</v>
+        <v>73.1822722990819</v>
       </c>
     </row>
     <row r="632">
@@ -10930,10 +10928,10 @@
         <v>10</v>
       </c>
       <c r="D632" t="n">
-        <v>509.628290443377</v>
+        <v>78.3965869882104</v>
       </c>
       <c r="E632" t="n">
-        <v>472.295449662074</v>
+        <v>73.8215655522058</v>
       </c>
     </row>
     <row r="633">
@@ -10947,10 +10945,10 @@
         <v>10</v>
       </c>
       <c r="D633" t="n">
-        <v>519.601716605958</v>
+        <v>79.3338637228056</v>
       </c>
       <c r="E633" t="n">
-        <v>478.492919065572</v>
+        <v>74.4881231785554</v>
       </c>
     </row>
     <row r="634">
@@ -10964,10 +10962,10 @@
         <v>10</v>
       </c>
       <c r="D634" t="n">
-        <v>516.937506249131</v>
+        <v>84.5133094829862</v>
       </c>
       <c r="E634" t="n">
-        <v>485.639891311769</v>
+        <v>75.2457729913469</v>
       </c>
     </row>
     <row r="635">
@@ -10981,10 +10979,10 @@
         <v>10</v>
       </c>
       <c r="D635" t="n">
-        <v>520.527024985972</v>
+        <v>88.7146181675197</v>
       </c>
       <c r="E635" t="n">
-        <v>492.382007334432</v>
+        <v>76.3497093875925</v>
       </c>
     </row>
     <row r="636">
@@ -10998,10 +10996,10 @@
         <v>10</v>
       </c>
       <c r="D636" t="n">
-        <v>515.442469851828</v>
+        <v>85.7281916964925</v>
       </c>
       <c r="E636" t="n">
-        <v>496.522738360214</v>
+        <v>77.261125345848</v>
       </c>
     </row>
     <row r="637">
@@ -11015,10 +11013,10 @@
         <v>10</v>
       </c>
       <c r="D637" t="n">
-        <v>524.994910636489</v>
+        <v>88.4269572167802</v>
       </c>
       <c r="E637" t="n">
-        <v>501.602666344537</v>
+        <v>78.1958740047225</v>
       </c>
     </row>
     <row r="638">
@@ -11032,10 +11030,10 @@
         <v>10</v>
       </c>
       <c r="D638" t="n">
-        <v>526.259524120097</v>
+        <v>87.1332821224828</v>
       </c>
       <c r="E638" t="n">
-        <v>506.37043939856</v>
+        <v>79.457266354642</v>
       </c>
     </row>
     <row r="639">
@@ -11049,10 +11047,10 @@
         <v>10</v>
       </c>
       <c r="D639" t="n">
-        <v>534.066355287013</v>
+        <v>83.1089646400721</v>
       </c>
       <c r="E639" t="n">
-        <v>511.12834205467</v>
+        <v>80.3789662606426</v>
       </c>
     </row>
     <row r="640">
@@ -11066,10 +11064,10 @@
         <v>10</v>
       </c>
       <c r="D640" t="n">
-        <v>551.41334486955</v>
+        <v>83.3510115253494</v>
       </c>
       <c r="E640" t="n">
-        <v>516.124201829745</v>
+        <v>81.3024222480451</v>
       </c>
     </row>
     <row r="641">
@@ -11083,10 +11081,10 @@
         <v>10</v>
       </c>
       <c r="D641" t="n">
-        <v>565.648740374858</v>
+        <v>83.5390377252012</v>
       </c>
       <c r="E641" t="n">
-        <v>522.773735902596</v>
+        <v>82.2339842876722</v>
       </c>
     </row>
     <row r="642">
@@ -11100,10 +11098,10 @@
         <v>10</v>
       </c>
       <c r="D642" t="n">
-        <v>541.827258679976</v>
+        <v>82.2559884588231</v>
       </c>
       <c r="E642" t="n">
-        <v>526.685760367041</v>
+        <v>83.0737265546589</v>
       </c>
     </row>
     <row r="643">
@@ -11117,10 +11115,10 @@
         <v>10</v>
       </c>
       <c r="D643" t="n">
-        <v>572.11627609767</v>
+        <v>82.2147518278186</v>
       </c>
       <c r="E643" t="n">
-        <v>533.20528485016</v>
+        <v>83.8930469645451</v>
       </c>
     </row>
     <row r="644">
@@ -11134,10 +11132,10 @@
         <v>10</v>
       </c>
       <c r="D644" t="n">
-        <v>568.560024403361</v>
+        <v>82.6688109920672</v>
       </c>
       <c r="E644" t="n">
-        <v>538.116262680159</v>
+        <v>84.2490656315332</v>
       </c>
     </row>
     <row r="645">
@@ -11151,10 +11149,10 @@
         <v>10</v>
       </c>
       <c r="D645" t="n">
-        <v>596.673521352048</v>
+        <v>87.9437961994899</v>
       </c>
       <c r="E645" t="n">
-        <v>544.538913075666</v>
+        <v>84.9665600045902</v>
       </c>
     </row>
     <row r="646">
@@ -11168,10 +11166,10 @@
         <v>10</v>
       </c>
       <c r="D646" t="n">
-        <v>588.38630961402</v>
+        <v>88.0851136989694</v>
       </c>
       <c r="E646" t="n">
-        <v>550.49298002274</v>
+        <v>85.2642103559222</v>
       </c>
     </row>
     <row r="647">
@@ -11185,10 +11183,10 @@
         <v>10</v>
       </c>
       <c r="D647" t="n">
-        <v>587.5265885206</v>
+        <v>90.9163173795506</v>
       </c>
       <c r="E647" t="n">
-        <v>556.076276983959</v>
+        <v>85.4476852902581</v>
       </c>
     </row>
     <row r="648">
@@ -11202,10 +11200,10 @@
         <v>10</v>
       </c>
       <c r="D648" t="n">
-        <v>580.478738543453</v>
+        <v>88.8353404449253</v>
       </c>
       <c r="E648" t="n">
-        <v>561.495966041595</v>
+        <v>85.7066143526275</v>
       </c>
     </row>
     <row r="649">
@@ -11219,10 +11217,10 @@
         <v>10</v>
       </c>
       <c r="D649" t="n">
-        <v>592.232176142912</v>
+        <v>88.3948578560411</v>
       </c>
       <c r="E649" t="n">
-        <v>567.099071500463</v>
+        <v>85.7039394058992</v>
       </c>
     </row>
     <row r="650">
@@ -11236,10 +11234,10 @@
         <v>10</v>
       </c>
       <c r="D650" t="n">
-        <v>602.774341298572</v>
+        <v>86.6295898779392</v>
       </c>
       <c r="E650" t="n">
-        <v>573.475306265336</v>
+        <v>85.6619650521873</v>
       </c>
     </row>
     <row r="651">
@@ -11253,10 +11251,10 @@
         <v>10</v>
       </c>
       <c r="D651" t="n">
-        <v>594.045648661934</v>
+        <v>82.5445852884514</v>
       </c>
       <c r="E651" t="n">
-        <v>578.473580713246</v>
+        <v>85.6149334395522</v>
       </c>
     </row>
     <row r="652">
@@ -11270,10 +11268,10 @@
         <v>10</v>
       </c>
       <c r="D652" t="n">
-        <v>608.24277687108</v>
+        <v>81.8254928445596</v>
       </c>
       <c r="E652" t="n">
-        <v>583.209366713374</v>
+        <v>85.4878068828197</v>
       </c>
     </row>
     <row r="653">
@@ -11287,10 +11285,10 @@
         <v>10</v>
       </c>
       <c r="D653" t="n">
-        <v>619.395300307819</v>
+        <v>81.7718638572031</v>
       </c>
       <c r="E653" t="n">
-        <v>587.688246707787</v>
+        <v>85.3405423938199</v>
       </c>
     </row>
     <row r="654">
@@ -11304,10 +11302,10 @@
         <v>10</v>
       </c>
       <c r="D654" t="n">
-        <v>627.326646036676</v>
+        <v>84.8647527996633</v>
       </c>
       <c r="E654" t="n">
-        <v>594.813195654179</v>
+        <v>85.5579394222232</v>
       </c>
     </row>
     <row r="655">
@@ -11321,10 +11319,10 @@
         <v>10</v>
       </c>
       <c r="D655" t="n">
-        <v>616.245382351534</v>
+        <v>83.8007302002446</v>
       </c>
       <c r="E655" t="n">
-        <v>598.490621175334</v>
+        <v>85.6901042865921</v>
       </c>
     </row>
     <row r="656">
@@ -11338,10 +11336,10 @@
         <v>10</v>
       </c>
       <c r="D656" t="n">
-        <v>637.584540565154</v>
+        <v>86.6652928096498</v>
       </c>
       <c r="E656" t="n">
-        <v>604.242664188817</v>
+        <v>86.0231444380573</v>
       </c>
     </row>
     <row r="657">
@@ -11355,10 +11353,10 @@
         <v>10</v>
       </c>
       <c r="D657" t="n">
-        <v>668.908690629811</v>
+        <v>85.9672754669865</v>
       </c>
       <c r="E657" t="n">
-        <v>610.26226162863</v>
+        <v>85.8584343770153</v>
       </c>
     </row>
     <row r="658">
@@ -11372,10 +11370,10 @@
         <v>10</v>
       </c>
       <c r="D658" t="n">
-        <v>655.204695938517</v>
+        <v>86.7309211162566</v>
       </c>
       <c r="E658" t="n">
-        <v>615.830460489005</v>
+        <v>85.7455849951226</v>
       </c>
     </row>
     <row r="659">
@@ -11389,10 +11387,10 @@
         <v>10</v>
       </c>
       <c r="D659" t="n">
-        <v>697.894933491495</v>
+        <v>87.6872921605799</v>
       </c>
       <c r="E659" t="n">
-        <v>625.027822569913</v>
+        <v>85.4764995602084</v>
       </c>
     </row>
     <row r="660">
@@ -11406,10 +11404,10 @@
         <v>10</v>
       </c>
       <c r="D660" t="n">
-        <v>676.856114915719</v>
+        <v>89.0247176902273</v>
       </c>
       <c r="E660" t="n">
-        <v>633.059270600935</v>
+        <v>85.4922809973169</v>
       </c>
     </row>
     <row r="661">
@@ -11423,10 +11421,10 @@
         <v>10</v>
       </c>
       <c r="D661" t="n">
-        <v>692.539150966401</v>
+        <v>88.4716230721895</v>
       </c>
       <c r="E661" t="n">
-        <v>641.418185169559</v>
+        <v>85.4986780986626</v>
       </c>
     </row>
     <row r="662">
@@ -11440,10 +11438,10 @@
         <v>10</v>
       </c>
       <c r="D662" t="n">
-        <v>713.855889224286</v>
+        <v>88.3883002240841</v>
       </c>
       <c r="E662" t="n">
-        <v>650.674980830036</v>
+        <v>85.6452372941746</v>
       </c>
     </row>
     <row r="663">
@@ -11457,10 +11455,10 @@
         <v>10</v>
       </c>
       <c r="D663" t="n">
-        <v>710.769912069582</v>
+        <v>91.9608852928247</v>
       </c>
       <c r="E663" t="n">
-        <v>660.402002780673</v>
+        <v>86.4299289612057</v>
       </c>
     </row>
     <row r="664">
@@ -11474,10 +11472,10 @@
         <v>10</v>
       </c>
       <c r="D664" t="n">
-        <v>705.447095046458</v>
+        <v>91.233334199971</v>
       </c>
       <c r="E664" t="n">
-        <v>668.502362628621</v>
+        <v>87.2139157408234</v>
       </c>
     </row>
     <row r="665">
@@ -11491,10 +11489,10 @@
         <v>10</v>
       </c>
       <c r="D665" t="n">
-        <v>712.762144593343</v>
+        <v>94.9818608631427</v>
       </c>
       <c r="E665" t="n">
-        <v>676.282932985748</v>
+        <v>88.3147488246517</v>
       </c>
     </row>
     <row r="666">
@@ -11508,10 +11506,10 @@
         <v>10</v>
       </c>
       <c r="D666" t="n">
-        <v>702.130595938762</v>
+        <v>93.2189455025761</v>
       </c>
       <c r="E666" t="n">
-        <v>682.516595477589</v>
+        <v>89.0109315498944</v>
       </c>
     </row>
     <row r="667">
@@ -11525,10 +11523,10 @@
         <v>10</v>
       </c>
       <c r="D667" t="n">
-        <v>715.217725407448</v>
+        <v>94.4923773273482</v>
       </c>
       <c r="E667" t="n">
-        <v>690.764290732248</v>
+        <v>89.9019021438197</v>
       </c>
     </row>
     <row r="668">
@@ -11542,10 +11540,10 @@
         <v>10</v>
       </c>
       <c r="D668" t="n">
-        <v>730.297790337836</v>
+        <v>94.7468304885008</v>
       </c>
       <c r="E668" t="n">
-        <v>698.490394879972</v>
+        <v>90.5753636170573</v>
       </c>
     </row>
     <row r="669">
@@ -11559,10 +11557,10 @@
         <v>10</v>
       </c>
       <c r="D669" t="n">
-        <v>746.919487920315</v>
+        <v>94.6504424021756</v>
       </c>
       <c r="E669" t="n">
-        <v>704.99129465418</v>
+        <v>91.2989608616564</v>
       </c>
     </row>
     <row r="670">
@@ -11576,10 +11574,10 @@
         <v>10</v>
       </c>
       <c r="D670" t="n">
-        <v>717.952534310826</v>
+        <v>97.542484196831</v>
       </c>
       <c r="E670" t="n">
-        <v>710.220281185206</v>
+        <v>92.1999244517042</v>
       </c>
     </row>
     <row r="671">
@@ -11593,10 +11591,10 @@
         <v>10</v>
       </c>
       <c r="D671" t="n">
-        <v>749.170131532343</v>
+        <v>100.047904360493</v>
       </c>
       <c r="E671" t="n">
-        <v>714.493214355277</v>
+        <v>93.2299754683637</v>
       </c>
     </row>
     <row r="672">
@@ -11610,10 +11608,10 @@
         <v>10</v>
       </c>
       <c r="D672" t="n">
-        <v>742.453357047643</v>
+        <v>105.289073057232</v>
       </c>
       <c r="E672" t="n">
-        <v>719.959651199604</v>
+        <v>94.5853384156141</v>
       </c>
     </row>
     <row r="673">
@@ -11627,10 +11625,10 @@
         <v>10</v>
       </c>
       <c r="D673" t="n">
-        <v>752.175277427282</v>
+        <v>104.539049909486</v>
       </c>
       <c r="E673" t="n">
-        <v>724.929328404677</v>
+        <v>95.9242906520554</v>
       </c>
     </row>
     <row r="674">
@@ -11644,10 +11642,10 @@
         <v>10</v>
       </c>
       <c r="D674" t="n">
-        <v>747.325260246612</v>
+        <v>104.638195728519</v>
       </c>
       <c r="E674" t="n">
-        <v>727.718442656537</v>
+        <v>97.2784486107583</v>
       </c>
     </row>
     <row r="675">
@@ -11661,10 +11659,10 @@
         <v>10</v>
       </c>
       <c r="D675" t="n">
-        <v>762.793090082814</v>
+        <v>106.616180652463</v>
       </c>
       <c r="E675" t="n">
-        <v>732.053707490973</v>
+        <v>98.4997232240615</v>
       </c>
     </row>
     <row r="676">
@@ -11678,10 +11676,10 @@
         <v>10</v>
       </c>
       <c r="D676" t="n">
-        <v>776.93591859858</v>
+        <v>106.603541318742</v>
       </c>
       <c r="E676" t="n">
-        <v>738.01110945365</v>
+        <v>99.7805738172924</v>
       </c>
     </row>
     <row r="677">
@@ -11695,10 +11693,10 @@
         <v>10</v>
       </c>
       <c r="D677" t="n">
-        <v>769.92813945386</v>
+        <v>106.559298914382</v>
       </c>
       <c r="E677" t="n">
-        <v>742.774942358693</v>
+        <v>100.745360321562</v>
       </c>
     </row>
     <row r="678">
@@ -11712,10 +11710,10 @@
         <v>10</v>
       </c>
       <c r="D678" t="n">
-        <v>788.654157951688</v>
+        <v>106.536546966904</v>
       </c>
       <c r="E678" t="n">
-        <v>749.985239193104</v>
+        <v>101.85516044359</v>
       </c>
     </row>
     <row r="679">
@@ -11729,10 +11727,10 @@
         <v>10</v>
       </c>
       <c r="D679" t="n">
-        <v>797.363651571224</v>
+        <v>109.385893336664</v>
       </c>
       <c r="E679" t="n">
-        <v>756.830733040085</v>
+        <v>103.096286777699</v>
       </c>
     </row>
     <row r="680">
@@ -12788,7 +12786,7 @@
         <v>1682.73226420873</v>
       </c>
       <c r="E745" t="n">
-        <v>1683.54016546354</v>
+        <v>1683.54016546355</v>
       </c>
     </row>
     <row r="746">
@@ -12890,7 +12888,7 @@
         <v>1768.65452680699</v>
       </c>
       <c r="E751" t="n">
-        <v>1713.90626542896</v>
+        <v>1713.90626542897</v>
       </c>
     </row>
     <row r="752">
@@ -13111,7 +13109,7 @@
         <v>1912.84111030334</v>
       </c>
       <c r="E764" t="n">
-        <v>1818.56442381287</v>
+        <v>1818.56442381286</v>
       </c>
     </row>
     <row r="765">
@@ -13417,7 +13415,7 @@
         <v>2047.34122485201</v>
       </c>
       <c r="E782" t="n">
-        <v>1995.40658162946</v>
+        <v>1995.40658162947</v>
       </c>
     </row>
     <row r="783">
@@ -13536,7 +13534,7 @@
         <v>2177.40146885074</v>
       </c>
       <c r="E789" t="n">
-        <v>2078.06766654672</v>
+        <v>2078.06766654673</v>
       </c>
     </row>
     <row r="790">
@@ -13587,7 +13585,7 @@
         <v>2240.01185308006</v>
       </c>
       <c r="E792" t="n">
-        <v>2118.10360738528</v>
+        <v>2118.10360738529</v>
       </c>
     </row>
     <row r="793">
@@ -13621,7 +13619,7 @@
         <v>2215.53172718359</v>
       </c>
       <c r="E794" t="n">
-        <v>2145.82144412593</v>
+        <v>2145.82144412594</v>
       </c>
     </row>
     <row r="795">
@@ -13672,7 +13670,7 @@
         <v>2264.54301979533</v>
       </c>
       <c r="E797" t="n">
-        <v>2189.91594828347</v>
+        <v>2189.91594828348</v>
       </c>
     </row>
     <row r="798">
